--- a/AAII_Financials/Yearly/YRD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/YRD_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -724,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>474300</v>
+        <v>477500</v>
       </c>
       <c r="E8" s="3">
-        <v>618300</v>
+        <v>622500</v>
       </c>
       <c r="F8" s="3">
-        <v>547100</v>
+        <v>550800</v>
       </c>
       <c r="G8" s="3">
-        <v>1211800</v>
+        <v>1220100</v>
       </c>
       <c r="H8" s="3">
-        <v>1644300</v>
+        <v>1655400</v>
       </c>
       <c r="I8" s="3">
-        <v>765400</v>
+        <v>770600</v>
       </c>
       <c r="J8" s="3">
-        <v>447100</v>
+        <v>450100</v>
       </c>
       <c r="K8" s="3">
         <v>30000</v>
@@ -766,25 +766,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>107300</v>
+        <v>108000</v>
       </c>
       <c r="E9" s="3">
-        <v>105100</v>
+        <v>105800</v>
       </c>
       <c r="F9" s="3">
-        <v>152500</v>
+        <v>153600</v>
       </c>
       <c r="G9" s="3">
-        <v>91800</v>
+        <v>92500</v>
       </c>
       <c r="H9" s="3">
-        <v>146500</v>
+        <v>147500</v>
       </c>
       <c r="I9" s="3">
-        <v>57700</v>
+        <v>58100</v>
       </c>
       <c r="J9" s="3">
-        <v>24900</v>
+        <v>25000</v>
       </c>
       <c r="K9" s="3">
         <v>2200</v>
@@ -808,25 +808,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>367000</v>
+        <v>369500</v>
       </c>
       <c r="E10" s="3">
-        <v>513300</v>
+        <v>516700</v>
       </c>
       <c r="F10" s="3">
-        <v>394500</v>
+        <v>397200</v>
       </c>
       <c r="G10" s="3">
-        <v>1120000</v>
+        <v>1127600</v>
       </c>
       <c r="H10" s="3">
-        <v>1497700</v>
+        <v>1507900</v>
       </c>
       <c r="I10" s="3">
-        <v>707700</v>
+        <v>712500</v>
       </c>
       <c r="J10" s="3">
-        <v>422200</v>
+        <v>425100</v>
       </c>
       <c r="K10" s="3">
         <v>27800</v>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>90600</v>
+        <v>91200</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>271000</v>
+        <v>272900</v>
       </c>
       <c r="E17" s="3">
-        <v>440600</v>
+        <v>443600</v>
       </c>
       <c r="F17" s="3">
-        <v>644500</v>
+        <v>648900</v>
       </c>
       <c r="G17" s="3">
-        <v>1034000</v>
+        <v>1041100</v>
       </c>
       <c r="H17" s="3">
-        <v>1445400</v>
+        <v>1455300</v>
       </c>
       <c r="I17" s="3">
-        <v>533800</v>
+        <v>537400</v>
       </c>
       <c r="J17" s="3">
-        <v>297300</v>
+        <v>299300</v>
       </c>
       <c r="K17" s="3">
         <v>20900</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>203200</v>
+        <v>204600</v>
       </c>
       <c r="E18" s="3">
-        <v>177800</v>
+        <v>179000</v>
       </c>
       <c r="F18" s="3">
-        <v>-97500</v>
+        <v>-98100</v>
       </c>
       <c r="G18" s="3">
-        <v>177800</v>
+        <v>179000</v>
       </c>
       <c r="H18" s="3">
-        <v>198800</v>
+        <v>200200</v>
       </c>
       <c r="I18" s="3">
-        <v>231600</v>
+        <v>233200</v>
       </c>
       <c r="J18" s="3">
-        <v>149800</v>
+        <v>150800</v>
       </c>
       <c r="K18" s="3">
         <v>9100</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="E20" s="3">
-        <v>-11600</v>
+        <v>-11700</v>
       </c>
       <c r="F20" s="3">
-        <v>-9300</v>
+        <v>-9400</v>
       </c>
       <c r="G20" s="3">
-        <v>14800</v>
+        <v>14900</v>
       </c>
       <c r="H20" s="3">
-        <v>46100</v>
+        <v>46400</v>
       </c>
       <c r="I20" s="3">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="J20" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>210100</v>
+        <v>211600</v>
       </c>
       <c r="E21" s="3">
-        <v>172100</v>
+        <v>173300</v>
       </c>
       <c r="F21" s="3">
-        <v>-94100</v>
+        <v>-94700</v>
       </c>
       <c r="G21" s="3">
-        <v>210000</v>
+        <v>211400</v>
       </c>
       <c r="H21" s="3">
-        <v>265400</v>
+        <v>267200</v>
       </c>
       <c r="I21" s="3">
-        <v>245300</v>
+        <v>247000</v>
       </c>
       <c r="J21" s="3">
-        <v>153700</v>
+        <v>154700</v>
       </c>
       <c r="K21" s="3">
         <v>9300</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>206500</v>
+        <v>207900</v>
       </c>
       <c r="E23" s="3">
-        <v>166100</v>
+        <v>167300</v>
       </c>
       <c r="F23" s="3">
-        <v>-106800</v>
+        <v>-107500</v>
       </c>
       <c r="G23" s="3">
-        <v>192600</v>
+        <v>193900</v>
       </c>
       <c r="H23" s="3">
-        <v>245000</v>
+        <v>246600</v>
       </c>
       <c r="I23" s="3">
-        <v>242100</v>
+        <v>243700</v>
       </c>
       <c r="J23" s="3">
-        <v>152200</v>
+        <v>153300</v>
       </c>
       <c r="K23" s="3">
         <v>9200</v>
@@ -1321,22 +1321,22 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>41500</v>
+        <v>41800</v>
       </c>
       <c r="E24" s="3">
-        <v>23500</v>
+        <v>23700</v>
       </c>
       <c r="F24" s="3">
-        <v>-11100</v>
+        <v>-11200</v>
       </c>
       <c r="G24" s="3">
-        <v>33000</v>
+        <v>33300</v>
       </c>
       <c r="H24" s="3">
-        <v>26800</v>
+        <v>27000</v>
       </c>
       <c r="I24" s="3">
-        <v>52600</v>
+        <v>53000</v>
       </c>
       <c r="J24" s="3">
         <v>-1900</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>165000</v>
+        <v>166100</v>
       </c>
       <c r="E26" s="3">
-        <v>142600</v>
+        <v>143600</v>
       </c>
       <c r="F26" s="3">
-        <v>-95700</v>
+        <v>-96300</v>
       </c>
       <c r="G26" s="3">
-        <v>159600</v>
+        <v>160700</v>
       </c>
       <c r="H26" s="3">
-        <v>218100</v>
+        <v>219600</v>
       </c>
       <c r="I26" s="3">
-        <v>189400</v>
+        <v>190700</v>
       </c>
       <c r="J26" s="3">
-        <v>154200</v>
+        <v>155200</v>
       </c>
       <c r="K26" s="3">
         <v>6300</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>165000</v>
+        <v>166100</v>
       </c>
       <c r="E27" s="3">
-        <v>142600</v>
+        <v>143600</v>
       </c>
       <c r="F27" s="3">
-        <v>-95700</v>
+        <v>-96300</v>
       </c>
       <c r="G27" s="3">
-        <v>159600</v>
+        <v>160700</v>
       </c>
       <c r="H27" s="3">
-        <v>218100</v>
+        <v>219600</v>
       </c>
       <c r="I27" s="3">
-        <v>189400</v>
+        <v>190700</v>
       </c>
       <c r="J27" s="3">
-        <v>154200</v>
+        <v>155200</v>
       </c>
       <c r="K27" s="3">
         <v>6300</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3200</v>
+        <v>-3300</v>
       </c>
       <c r="E32" s="3">
-        <v>11600</v>
+        <v>11700</v>
       </c>
       <c r="F32" s="3">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="G32" s="3">
-        <v>-14800</v>
+        <v>-14900</v>
       </c>
       <c r="H32" s="3">
-        <v>-46100</v>
+        <v>-46400</v>
       </c>
       <c r="I32" s="3">
-        <v>-10400</v>
+        <v>-10500</v>
       </c>
       <c r="J32" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>165000</v>
+        <v>166100</v>
       </c>
       <c r="E33" s="3">
-        <v>142600</v>
+        <v>143600</v>
       </c>
       <c r="F33" s="3">
-        <v>-95700</v>
+        <v>-96300</v>
       </c>
       <c r="G33" s="3">
-        <v>159600</v>
+        <v>160700</v>
       </c>
       <c r="H33" s="3">
-        <v>218100</v>
+        <v>219600</v>
       </c>
       <c r="I33" s="3">
-        <v>189400</v>
+        <v>190700</v>
       </c>
       <c r="J33" s="3">
-        <v>154200</v>
+        <v>155200</v>
       </c>
       <c r="K33" s="3">
         <v>6300</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>165000</v>
+        <v>166100</v>
       </c>
       <c r="E35" s="3">
-        <v>142600</v>
+        <v>143600</v>
       </c>
       <c r="F35" s="3">
-        <v>-95700</v>
+        <v>-96300</v>
       </c>
       <c r="G35" s="3">
-        <v>159600</v>
+        <v>160700</v>
       </c>
       <c r="H35" s="3">
-        <v>218100</v>
+        <v>219600</v>
       </c>
       <c r="I35" s="3">
-        <v>189400</v>
+        <v>190700</v>
       </c>
       <c r="J35" s="3">
-        <v>154200</v>
+        <v>155200</v>
       </c>
       <c r="K35" s="3">
         <v>6300</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>589900</v>
+        <v>593900</v>
       </c>
       <c r="E41" s="3">
-        <v>395500</v>
+        <v>398200</v>
       </c>
       <c r="F41" s="3">
-        <v>341000</v>
+        <v>343400</v>
       </c>
       <c r="G41" s="3">
-        <v>441600</v>
+        <v>444600</v>
       </c>
       <c r="H41" s="3">
-        <v>360000</v>
+        <v>362400</v>
       </c>
       <c r="I41" s="3">
-        <v>256400</v>
+        <v>258200</v>
       </c>
       <c r="J41" s="3">
-        <v>133700</v>
+        <v>134600</v>
       </c>
       <c r="K41" s="3">
         <v>18800</v>
@@ -1992,22 +1992,22 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>213000</v>
+        <v>214500</v>
       </c>
       <c r="E43" s="3">
-        <v>175100</v>
+        <v>176300</v>
       </c>
       <c r="F43" s="3">
-        <v>159100</v>
+        <v>160200</v>
       </c>
       <c r="G43" s="3">
-        <v>222800</v>
+        <v>224300</v>
       </c>
       <c r="H43" s="3">
-        <v>253900</v>
+        <v>255600</v>
       </c>
       <c r="I43" s="3">
-        <v>19100</v>
+        <v>19300</v>
       </c>
       <c r="J43" s="3">
         <v>4200</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>32200</v>
+        <v>32400</v>
       </c>
       <c r="E45" s="3">
-        <v>35300</v>
+        <v>35500</v>
       </c>
       <c r="F45" s="3">
-        <v>15100</v>
+        <v>15200</v>
       </c>
       <c r="G45" s="3">
-        <v>27000</v>
+        <v>27200</v>
       </c>
       <c r="H45" s="3">
-        <v>369100</v>
+        <v>371600</v>
       </c>
       <c r="I45" s="3">
-        <v>147600</v>
+        <v>148600</v>
       </c>
       <c r="J45" s="3">
-        <v>64500</v>
+        <v>64900</v>
       </c>
       <c r="K45" s="3">
         <v>5500</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>299700</v>
+        <v>301800</v>
       </c>
       <c r="E47" s="3">
-        <v>422100</v>
+        <v>425000</v>
       </c>
       <c r="F47" s="3">
-        <v>327900</v>
+        <v>330100</v>
       </c>
       <c r="G47" s="3">
-        <v>528900</v>
+        <v>532500</v>
       </c>
       <c r="H47" s="3">
-        <v>944400</v>
+        <v>950800</v>
       </c>
       <c r="I47" s="3">
-        <v>243700</v>
+        <v>245400</v>
       </c>
       <c r="J47" s="3">
-        <v>224800</v>
+        <v>226300</v>
       </c>
       <c r="K47" s="3">
         <v>5600</v>
@@ -2202,19 +2202,19 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>15300</v>
+        <v>15500</v>
       </c>
       <c r="E48" s="3">
-        <v>25300</v>
+        <v>25500</v>
       </c>
       <c r="F48" s="3">
-        <v>34900</v>
+        <v>35200</v>
       </c>
       <c r="G48" s="3">
-        <v>73200</v>
+        <v>73700</v>
       </c>
       <c r="H48" s="3">
-        <v>49100</v>
+        <v>49500</v>
       </c>
       <c r="I48" s="3">
         <v>11400</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>23900</v>
+        <v>24000</v>
       </c>
       <c r="E52" s="3">
-        <v>12200</v>
+        <v>12300</v>
       </c>
       <c r="F52" s="3">
-        <v>35100</v>
+        <v>35300</v>
       </c>
       <c r="G52" s="3">
-        <v>16100</v>
+        <v>16200</v>
       </c>
       <c r="H52" s="3">
-        <v>84500</v>
+        <v>85000</v>
       </c>
       <c r="I52" s="3">
-        <v>359900</v>
+        <v>362400</v>
       </c>
       <c r="J52" s="3">
-        <v>228500</v>
+        <v>230000</v>
       </c>
       <c r="K52" s="3">
         <v>14600</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1178700</v>
+        <v>1186700</v>
       </c>
       <c r="E54" s="3">
-        <v>1068700</v>
+        <v>1075900</v>
       </c>
       <c r="F54" s="3">
-        <v>925400</v>
+        <v>931700</v>
       </c>
       <c r="G54" s="3">
-        <v>1331700</v>
+        <v>1340800</v>
       </c>
       <c r="H54" s="3">
-        <v>1967900</v>
+        <v>1981300</v>
       </c>
       <c r="I54" s="3">
-        <v>1038200</v>
+        <v>1045200</v>
       </c>
       <c r="J54" s="3">
-        <v>660500</v>
+        <v>665000</v>
       </c>
       <c r="K54" s="3">
         <v>48600</v>
@@ -2535,16 +2535,16 @@
         <v>2000</v>
       </c>
       <c r="E57" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="F57" s="3">
         <v>1400</v>
       </c>
       <c r="G57" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="H57" s="3">
-        <v>42400</v>
+        <v>42700</v>
       </c>
       <c r="I57" s="3">
         <v>4700</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>217900</v>
+        <v>219400</v>
       </c>
       <c r="E59" s="3">
-        <v>240200</v>
+        <v>241900</v>
       </c>
       <c r="F59" s="3">
-        <v>319500</v>
+        <v>321700</v>
       </c>
       <c r="G59" s="3">
-        <v>374100</v>
+        <v>376600</v>
       </c>
       <c r="H59" s="3">
-        <v>1655900</v>
+        <v>1667200</v>
       </c>
       <c r="I59" s="3">
-        <v>205300</v>
+        <v>206700</v>
       </c>
       <c r="J59" s="3">
-        <v>195100</v>
+        <v>196500</v>
       </c>
       <c r="K59" s="3">
         <v>12100</v>
@@ -2700,19 +2700,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>106000</v>
+        <v>106800</v>
       </c>
       <c r="E61" s="3">
-        <v>142000</v>
+        <v>143000</v>
       </c>
       <c r="F61" s="3">
-        <v>69100</v>
+        <v>69600</v>
       </c>
       <c r="G61" s="3">
         <v>2600</v>
       </c>
       <c r="H61" s="3">
-        <v>26600</v>
+        <v>26800</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2742,19 +2742,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>11000</v>
+        <v>11100</v>
       </c>
       <c r="E62" s="3">
-        <v>15500</v>
+        <v>15600</v>
       </c>
       <c r="F62" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G62" s="3">
-        <v>30200</v>
+        <v>30400</v>
       </c>
       <c r="H62" s="3">
-        <v>67200</v>
+        <v>67700</v>
       </c>
       <c r="I62" s="3">
         <v>1600</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>345900</v>
+        <v>348300</v>
       </c>
       <c r="E66" s="3">
-        <v>402900</v>
+        <v>405700</v>
       </c>
       <c r="F66" s="3">
-        <v>403800</v>
+        <v>406600</v>
       </c>
       <c r="G66" s="3">
-        <v>711700</v>
+        <v>716600</v>
       </c>
       <c r="H66" s="3">
-        <v>2018100</v>
+        <v>2031800</v>
       </c>
       <c r="I66" s="3">
-        <v>628100</v>
+        <v>632300</v>
       </c>
       <c r="J66" s="3">
-        <v>365000</v>
+        <v>367500</v>
       </c>
       <c r="K66" s="3">
         <v>26900</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>125500</v>
+        <v>126400</v>
       </c>
       <c r="E72" s="3">
-        <v>-34200</v>
+        <v>-34500</v>
       </c>
       <c r="F72" s="3">
-        <v>-173600</v>
+        <v>-174800</v>
       </c>
       <c r="G72" s="3">
-        <v>-73700</v>
+        <v>-74200</v>
       </c>
       <c r="H72" s="3">
-        <v>295100</v>
+        <v>297100</v>
       </c>
       <c r="I72" s="3">
-        <v>253400</v>
+        <v>255100</v>
       </c>
       <c r="J72" s="3">
-        <v>162500</v>
+        <v>163600</v>
       </c>
       <c r="K72" s="3">
         <v>4200</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>832700</v>
+        <v>838400</v>
       </c>
       <c r="E76" s="3">
-        <v>665700</v>
+        <v>670300</v>
       </c>
       <c r="F76" s="3">
-        <v>521600</v>
+        <v>525200</v>
       </c>
       <c r="G76" s="3">
-        <v>620000</v>
+        <v>624200</v>
       </c>
       <c r="H76" s="3">
-        <v>-50200</v>
+        <v>-50500</v>
       </c>
       <c r="I76" s="3">
-        <v>410100</v>
+        <v>412900</v>
       </c>
       <c r="J76" s="3">
-        <v>295500</v>
+        <v>297500</v>
       </c>
       <c r="K76" s="3">
         <v>21700</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>165000</v>
+        <v>166100</v>
       </c>
       <c r="E81" s="3">
-        <v>142600</v>
+        <v>143600</v>
       </c>
       <c r="F81" s="3">
-        <v>-95700</v>
+        <v>-96300</v>
       </c>
       <c r="G81" s="3">
-        <v>159600</v>
+        <v>160700</v>
       </c>
       <c r="H81" s="3">
-        <v>218100</v>
+        <v>219600</v>
       </c>
       <c r="I81" s="3">
-        <v>189400</v>
+        <v>190700</v>
       </c>
       <c r="J81" s="3">
-        <v>154200</v>
+        <v>155200</v>
       </c>
       <c r="K81" s="3">
         <v>6300</v>
@@ -3497,19 +3497,19 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="E83" s="3">
         <v>6000</v>
       </c>
       <c r="F83" s="3">
-        <v>12700</v>
+        <v>12800</v>
       </c>
       <c r="G83" s="3">
-        <v>17400</v>
+        <v>17500</v>
       </c>
       <c r="H83" s="3">
-        <v>20400</v>
+        <v>20600</v>
       </c>
       <c r="I83" s="3">
         <v>3300</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>255400</v>
+        <v>257100</v>
       </c>
       <c r="E89" s="3">
-        <v>21800</v>
+        <v>22000</v>
       </c>
       <c r="F89" s="3">
-        <v>38900</v>
+        <v>39200</v>
       </c>
       <c r="G89" s="3">
-        <v>37900</v>
+        <v>38100</v>
       </c>
       <c r="H89" s="3">
-        <v>-546700</v>
+        <v>-550400</v>
       </c>
       <c r="I89" s="3">
-        <v>375100</v>
+        <v>377600</v>
       </c>
       <c r="J89" s="3">
-        <v>291800</v>
+        <v>293800</v>
       </c>
       <c r="K89" s="3">
         <v>8600</v>
@@ -3818,16 +3818,16 @@
         <v>-1900</v>
       </c>
       <c r="G91" s="3">
-        <v>-6600</v>
+        <v>-6700</v>
       </c>
       <c r="H91" s="3">
-        <v>-19400</v>
+        <v>-19600</v>
       </c>
       <c r="I91" s="3">
-        <v>-9700</v>
+        <v>-9800</v>
       </c>
       <c r="J91" s="3">
-        <v>-4100</v>
+        <v>-4200</v>
       </c>
       <c r="K91" s="3">
         <v>-400</v>
@@ -3938,22 +3938,22 @@
         <v>7300</v>
       </c>
       <c r="E94" s="3">
-        <v>-47800</v>
+        <v>-48200</v>
       </c>
       <c r="F94" s="3">
-        <v>-248100</v>
+        <v>-249800</v>
       </c>
       <c r="G94" s="3">
-        <v>153300</v>
+        <v>154300</v>
       </c>
       <c r="H94" s="3">
-        <v>455300</v>
+        <v>458400</v>
       </c>
       <c r="I94" s="3">
-        <v>-51700</v>
+        <v>-52100</v>
       </c>
       <c r="J94" s="3">
-        <v>-196300</v>
+        <v>-197600</v>
       </c>
       <c r="K94" s="3">
         <v>-6500</v>
@@ -4007,10 +4007,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-14700</v>
+        <v>-14800</v>
       </c>
       <c r="I96" s="3">
-        <v>-83600</v>
+        <v>-84100</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-67500</v>
+        <v>-68000</v>
       </c>
       <c r="E100" s="3">
-        <v>59000</v>
+        <v>59400</v>
       </c>
       <c r="F100" s="3">
-        <v>131900</v>
+        <v>132800</v>
       </c>
       <c r="G100" s="3">
-        <v>-158800</v>
+        <v>-159800</v>
       </c>
       <c r="H100" s="3">
-        <v>-108800</v>
+        <v>-109600</v>
       </c>
       <c r="I100" s="3">
-        <v>-117300</v>
+        <v>-118100</v>
       </c>
       <c r="J100" s="3">
-        <v>18700</v>
+        <v>18800</v>
       </c>
       <c r="K100" s="3">
         <v>16800</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>195400</v>
+        <v>196800</v>
       </c>
       <c r="E102" s="3">
-        <v>32900</v>
+        <v>33100</v>
       </c>
       <c r="F102" s="3">
-        <v>-77600</v>
+        <v>-78100</v>
       </c>
       <c r="G102" s="3">
-        <v>32400</v>
+        <v>32600</v>
       </c>
       <c r="H102" s="3">
-        <v>-199600</v>
+        <v>-201000</v>
       </c>
       <c r="I102" s="3">
-        <v>203900</v>
+        <v>205200</v>
       </c>
       <c r="J102" s="3">
-        <v>118300</v>
+        <v>119100</v>
       </c>
       <c r="K102" s="3">
         <v>18700</v>

--- a/AAII_Financials/Yearly/YRD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/YRD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>YRD</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>477500</v>
+        <v>676400</v>
       </c>
       <c r="E8" s="3">
-        <v>622500</v>
+        <v>474500</v>
       </c>
       <c r="F8" s="3">
-        <v>550800</v>
+        <v>618700</v>
       </c>
       <c r="G8" s="3">
-        <v>1220100</v>
+        <v>547400</v>
       </c>
       <c r="H8" s="3">
-        <v>1655400</v>
+        <v>1212500</v>
       </c>
       <c r="I8" s="3">
-        <v>770600</v>
+        <v>1645200</v>
       </c>
       <c r="J8" s="3">
+        <v>765900</v>
+      </c>
+      <c r="K8" s="3">
         <v>450100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>500</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>108000</v>
+        <v>134900</v>
       </c>
       <c r="E9" s="3">
-        <v>105800</v>
+        <v>107300</v>
       </c>
       <c r="F9" s="3">
-        <v>153600</v>
+        <v>105100</v>
       </c>
       <c r="G9" s="3">
-        <v>92500</v>
+        <v>152600</v>
       </c>
       <c r="H9" s="3">
-        <v>147500</v>
+        <v>91900</v>
       </c>
       <c r="I9" s="3">
-        <v>58100</v>
+        <v>146600</v>
       </c>
       <c r="J9" s="3">
+        <v>57700</v>
+      </c>
+      <c r="K9" s="3">
         <v>25000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>369500</v>
+        <v>541500</v>
       </c>
       <c r="E10" s="3">
-        <v>516700</v>
+        <v>367200</v>
       </c>
       <c r="F10" s="3">
-        <v>397200</v>
+        <v>513600</v>
       </c>
       <c r="G10" s="3">
-        <v>1127600</v>
+        <v>394800</v>
       </c>
       <c r="H10" s="3">
-        <v>1507900</v>
+        <v>1120600</v>
       </c>
       <c r="I10" s="3">
-        <v>712500</v>
+        <v>1498600</v>
       </c>
       <c r="J10" s="3">
+        <v>708100</v>
+      </c>
+      <c r="K10" s="3">
         <v>425100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>27800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>300</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,13 +874,14 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>20600</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>3</v>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,23 +961,26 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>91200</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>90600</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -978,8 +997,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -987,9 +1006,12 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>272900</v>
+        <v>317900</v>
       </c>
       <c r="E17" s="3">
-        <v>443600</v>
+        <v>271200</v>
       </c>
       <c r="F17" s="3">
-        <v>648900</v>
+        <v>440800</v>
       </c>
       <c r="G17" s="3">
-        <v>1041100</v>
+        <v>644900</v>
       </c>
       <c r="H17" s="3">
-        <v>1455300</v>
+        <v>1034600</v>
       </c>
       <c r="I17" s="3">
-        <v>537400</v>
+        <v>1446300</v>
       </c>
       <c r="J17" s="3">
+        <v>534100</v>
+      </c>
+      <c r="K17" s="3">
         <v>299300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1800</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>204600</v>
+        <v>358500</v>
       </c>
       <c r="E18" s="3">
-        <v>179000</v>
+        <v>203400</v>
       </c>
       <c r="F18" s="3">
-        <v>-98100</v>
+        <v>177900</v>
       </c>
       <c r="G18" s="3">
-        <v>179000</v>
+        <v>-97500</v>
       </c>
       <c r="H18" s="3">
-        <v>200200</v>
+        <v>177900</v>
       </c>
       <c r="I18" s="3">
-        <v>233200</v>
+        <v>199000</v>
       </c>
       <c r="J18" s="3">
+        <v>231700</v>
+      </c>
+      <c r="K18" s="3">
         <v>150800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1300</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,92 +1179,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3300</v>
+        <v>7000</v>
       </c>
       <c r="E20" s="3">
-        <v>-11700</v>
+        <v>3200</v>
       </c>
       <c r="F20" s="3">
-        <v>-9400</v>
+        <v>-11600</v>
       </c>
       <c r="G20" s="3">
-        <v>14900</v>
+        <v>-9300</v>
       </c>
       <c r="H20" s="3">
-        <v>46400</v>
+        <v>14800</v>
       </c>
       <c r="I20" s="3">
-        <v>10500</v>
+        <v>46200</v>
       </c>
       <c r="J20" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K20" s="3">
         <v>2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>211600</v>
+        <v>366500</v>
       </c>
       <c r="E21" s="3">
-        <v>173300</v>
+        <v>210200</v>
       </c>
       <c r="F21" s="3">
-        <v>-94700</v>
+        <v>172200</v>
       </c>
       <c r="G21" s="3">
-        <v>211400</v>
+        <v>-94200</v>
       </c>
       <c r="H21" s="3">
-        <v>267200</v>
+        <v>210100</v>
       </c>
       <c r="I21" s="3">
-        <v>247000</v>
+        <v>265500</v>
       </c>
       <c r="J21" s="3">
+        <v>245500</v>
+      </c>
+      <c r="K21" s="3">
         <v>154700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1300</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1272,93 +1311,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>207900</v>
+        <v>365500</v>
       </c>
       <c r="E23" s="3">
-        <v>167300</v>
+        <v>206600</v>
       </c>
       <c r="F23" s="3">
-        <v>-107500</v>
+        <v>166200</v>
       </c>
       <c r="G23" s="3">
-        <v>193900</v>
+        <v>-106800</v>
       </c>
       <c r="H23" s="3">
-        <v>246600</v>
+        <v>192700</v>
       </c>
       <c r="I23" s="3">
-        <v>243700</v>
+        <v>245100</v>
       </c>
       <c r="J23" s="3">
+        <v>242200</v>
+      </c>
+      <c r="K23" s="3">
         <v>153300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1300</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>41800</v>
+        <v>78100</v>
       </c>
       <c r="E24" s="3">
-        <v>23700</v>
+        <v>41500</v>
       </c>
       <c r="F24" s="3">
-        <v>-11200</v>
+        <v>23500</v>
       </c>
       <c r="G24" s="3">
-        <v>33300</v>
+        <v>-11100</v>
       </c>
       <c r="H24" s="3">
-        <v>27000</v>
+        <v>33100</v>
       </c>
       <c r="I24" s="3">
-        <v>53000</v>
+        <v>26800</v>
       </c>
       <c r="J24" s="3">
+        <v>52700</v>
+      </c>
+      <c r="K24" s="3">
         <v>-1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2900</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>166100</v>
+        <v>287400</v>
       </c>
       <c r="E26" s="3">
-        <v>143600</v>
+        <v>165100</v>
       </c>
       <c r="F26" s="3">
-        <v>-96300</v>
+        <v>142700</v>
       </c>
       <c r="G26" s="3">
-        <v>160700</v>
+        <v>-95700</v>
       </c>
       <c r="H26" s="3">
-        <v>219600</v>
+        <v>159700</v>
       </c>
       <c r="I26" s="3">
-        <v>190700</v>
+        <v>218300</v>
       </c>
       <c r="J26" s="3">
+        <v>189500</v>
+      </c>
+      <c r="K26" s="3">
         <v>155200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1300</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>166100</v>
+        <v>287400</v>
       </c>
       <c r="E27" s="3">
-        <v>143600</v>
+        <v>165100</v>
       </c>
       <c r="F27" s="3">
-        <v>-96300</v>
+        <v>142700</v>
       </c>
       <c r="G27" s="3">
-        <v>160700</v>
+        <v>-95700</v>
       </c>
       <c r="H27" s="3">
-        <v>219600</v>
+        <v>159700</v>
       </c>
       <c r="I27" s="3">
-        <v>190700</v>
+        <v>218300</v>
       </c>
       <c r="J27" s="3">
+        <v>189500</v>
+      </c>
+      <c r="K27" s="3">
         <v>155200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1300</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3300</v>
+        <v>-7000</v>
       </c>
       <c r="E32" s="3">
-        <v>11700</v>
+        <v>-3200</v>
       </c>
       <c r="F32" s="3">
-        <v>9400</v>
+        <v>11600</v>
       </c>
       <c r="G32" s="3">
-        <v>-14900</v>
+        <v>9300</v>
       </c>
       <c r="H32" s="3">
-        <v>-46400</v>
+        <v>-14800</v>
       </c>
       <c r="I32" s="3">
-        <v>-10500</v>
+        <v>-46200</v>
       </c>
       <c r="J32" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>166100</v>
+        <v>287400</v>
       </c>
       <c r="E33" s="3">
-        <v>143600</v>
+        <v>165100</v>
       </c>
       <c r="F33" s="3">
-        <v>-96300</v>
+        <v>142700</v>
       </c>
       <c r="G33" s="3">
-        <v>160700</v>
+        <v>-95700</v>
       </c>
       <c r="H33" s="3">
-        <v>219600</v>
+        <v>159700</v>
       </c>
       <c r="I33" s="3">
-        <v>190700</v>
+        <v>218300</v>
       </c>
       <c r="J33" s="3">
+        <v>189500</v>
+      </c>
+      <c r="K33" s="3">
         <v>155200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1300</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>166100</v>
+        <v>287400</v>
       </c>
       <c r="E35" s="3">
-        <v>143600</v>
+        <v>165100</v>
       </c>
       <c r="F35" s="3">
-        <v>-96300</v>
+        <v>142700</v>
       </c>
       <c r="G35" s="3">
-        <v>160700</v>
+        <v>-95700</v>
       </c>
       <c r="H35" s="3">
-        <v>219600</v>
+        <v>159700</v>
       </c>
       <c r="I35" s="3">
-        <v>190700</v>
+        <v>218300</v>
       </c>
       <c r="J35" s="3">
+        <v>189500</v>
+      </c>
+      <c r="K35" s="3">
         <v>155200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1300</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,50 +1987,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>593900</v>
+        <v>800100</v>
       </c>
       <c r="E41" s="3">
-        <v>398200</v>
+        <v>590200</v>
       </c>
       <c r="F41" s="3">
-        <v>343400</v>
+        <v>395800</v>
       </c>
       <c r="G41" s="3">
-        <v>444600</v>
+        <v>341200</v>
       </c>
       <c r="H41" s="3">
-        <v>362400</v>
+        <v>441800</v>
       </c>
       <c r="I41" s="3">
-        <v>258200</v>
+        <v>360200</v>
       </c>
       <c r="J41" s="3">
+        <v>256600</v>
+      </c>
+      <c r="K41" s="3">
         <v>134600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18800</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
       <c r="M41" s="3">
         <v>0</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
+      <c r="N41" s="3">
+        <v>0</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1985,51 +2074,57 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>214500</v>
+        <v>190000</v>
       </c>
       <c r="E43" s="3">
-        <v>176300</v>
+        <v>213200</v>
       </c>
       <c r="F43" s="3">
-        <v>160200</v>
+        <v>175200</v>
       </c>
       <c r="G43" s="3">
-        <v>224300</v>
+        <v>159200</v>
       </c>
       <c r="H43" s="3">
-        <v>255600</v>
+        <v>222900</v>
       </c>
       <c r="I43" s="3">
-        <v>19300</v>
+        <v>254000</v>
       </c>
       <c r="J43" s="3">
+        <v>19100</v>
+      </c>
+      <c r="K43" s="3">
         <v>4200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>600</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2069,51 +2164,57 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>32400</v>
+        <v>48400</v>
       </c>
       <c r="E45" s="3">
-        <v>35500</v>
+        <v>32200</v>
       </c>
       <c r="F45" s="3">
-        <v>15200</v>
+        <v>35300</v>
       </c>
       <c r="G45" s="3">
-        <v>27200</v>
+        <v>15100</v>
       </c>
       <c r="H45" s="3">
-        <v>371600</v>
+        <v>27100</v>
       </c>
       <c r="I45" s="3">
-        <v>148600</v>
+        <v>369300</v>
       </c>
       <c r="J45" s="3">
+        <v>147700</v>
+      </c>
+      <c r="K45" s="3">
         <v>64900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>100</v>
       </c>
       <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
+      <c r="N45" s="3">
+        <v>100</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2153,93 +2254,102 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>301800</v>
+        <v>317300</v>
       </c>
       <c r="E47" s="3">
-        <v>425000</v>
+        <v>299900</v>
       </c>
       <c r="F47" s="3">
-        <v>330100</v>
+        <v>422400</v>
       </c>
       <c r="G47" s="3">
-        <v>532500</v>
+        <v>328100</v>
       </c>
       <c r="H47" s="3">
-        <v>950800</v>
+        <v>529200</v>
       </c>
       <c r="I47" s="3">
-        <v>245400</v>
+        <v>944900</v>
       </c>
       <c r="J47" s="3">
+        <v>243800</v>
+      </c>
+      <c r="K47" s="3">
         <v>226300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>100</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
+      <c r="N47" s="3">
+        <v>0</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>15500</v>
+        <v>14200</v>
       </c>
       <c r="E48" s="3">
-        <v>25500</v>
+        <v>15400</v>
       </c>
       <c r="F48" s="3">
-        <v>35200</v>
+        <v>25300</v>
       </c>
       <c r="G48" s="3">
-        <v>73700</v>
+        <v>34900</v>
       </c>
       <c r="H48" s="3">
-        <v>49500</v>
+        <v>73200</v>
       </c>
       <c r="I48" s="3">
+        <v>49200</v>
+      </c>
+      <c r="J48" s="3">
         <v>11400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>100</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
+      <c r="N48" s="3">
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,39 +2479,42 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>24000</v>
+        <v>47100</v>
       </c>
       <c r="E52" s="3">
-        <v>12300</v>
+        <v>23900</v>
       </c>
       <c r="F52" s="3">
-        <v>35300</v>
+        <v>12200</v>
       </c>
       <c r="G52" s="3">
-        <v>16200</v>
+        <v>35100</v>
       </c>
       <c r="H52" s="3">
-        <v>85000</v>
+        <v>16100</v>
       </c>
       <c r="I52" s="3">
-        <v>362400</v>
+        <v>84500</v>
       </c>
       <c r="J52" s="3">
+        <v>360200</v>
+      </c>
+      <c r="K52" s="3">
         <v>230000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14600</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2405,9 +2524,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1186700</v>
+        <v>1419900</v>
       </c>
       <c r="E54" s="3">
-        <v>1075900</v>
+        <v>1179300</v>
       </c>
       <c r="F54" s="3">
-        <v>931700</v>
+        <v>1069300</v>
       </c>
       <c r="G54" s="3">
-        <v>1340800</v>
+        <v>926000</v>
       </c>
       <c r="H54" s="3">
-        <v>1981300</v>
+        <v>1332500</v>
       </c>
       <c r="I54" s="3">
-        <v>1045200</v>
+        <v>1969000</v>
       </c>
       <c r="J54" s="3">
+        <v>1038800</v>
+      </c>
+      <c r="K54" s="3">
         <v>665000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>48600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>800</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,38 +2655,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
-        <v>2700</v>
-      </c>
       <c r="F57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
-        <v>6100</v>
-      </c>
       <c r="H57" s="3">
-        <v>42700</v>
+        <v>6000</v>
       </c>
       <c r="I57" s="3">
+        <v>42400</v>
+      </c>
+      <c r="J57" s="3">
         <v>4700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,9 +2697,12 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2609,51 +2742,57 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>219400</v>
+        <v>274200</v>
       </c>
       <c r="E59" s="3">
-        <v>241900</v>
+        <v>218000</v>
       </c>
       <c r="F59" s="3">
-        <v>321700</v>
+        <v>240400</v>
       </c>
       <c r="G59" s="3">
-        <v>376600</v>
+        <v>319700</v>
       </c>
       <c r="H59" s="3">
-        <v>1667200</v>
+        <v>374300</v>
       </c>
       <c r="I59" s="3">
-        <v>206700</v>
+        <v>1656800</v>
       </c>
       <c r="J59" s="3">
+        <v>205400</v>
+      </c>
+      <c r="K59" s="3">
         <v>196500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>300</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2693,29 +2832,32 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>106800</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>143000</v>
+        <v>106100</v>
       </c>
       <c r="F61" s="3">
-        <v>69600</v>
+        <v>142100</v>
       </c>
       <c r="G61" s="3">
+        <v>69100</v>
+      </c>
+      <c r="H61" s="3">
         <v>2600</v>
       </c>
-      <c r="H61" s="3">
-        <v>26800</v>
-      </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>26600</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2735,33 +2877,36 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>11100</v>
+        <v>16900</v>
       </c>
       <c r="E62" s="3">
-        <v>15600</v>
+        <v>11000</v>
       </c>
       <c r="F62" s="3">
+        <v>15500</v>
+      </c>
+      <c r="G62" s="3">
         <v>5400</v>
       </c>
-      <c r="G62" s="3">
-        <v>30400</v>
-      </c>
       <c r="H62" s="3">
-        <v>67700</v>
+        <v>30200</v>
       </c>
       <c r="I62" s="3">
+        <v>67300</v>
+      </c>
+      <c r="J62" s="3">
         <v>1600</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>348300</v>
+        <v>302800</v>
       </c>
       <c r="E66" s="3">
-        <v>405700</v>
+        <v>346100</v>
       </c>
       <c r="F66" s="3">
-        <v>406600</v>
+        <v>403200</v>
       </c>
       <c r="G66" s="3">
-        <v>716600</v>
+        <v>404100</v>
       </c>
       <c r="H66" s="3">
-        <v>2031800</v>
+        <v>712100</v>
       </c>
       <c r="I66" s="3">
-        <v>632300</v>
+        <v>2019200</v>
       </c>
       <c r="J66" s="3">
+        <v>628400</v>
+      </c>
+      <c r="K66" s="3">
         <v>367500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>300</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>126400</v>
+        <v>412500</v>
       </c>
       <c r="E72" s="3">
-        <v>-34500</v>
+        <v>125600</v>
       </c>
       <c r="F72" s="3">
-        <v>-174800</v>
+        <v>-34200</v>
       </c>
       <c r="G72" s="3">
-        <v>-74200</v>
+        <v>-173700</v>
       </c>
       <c r="H72" s="3">
-        <v>297100</v>
+        <v>-73700</v>
       </c>
       <c r="I72" s="3">
-        <v>255100</v>
+        <v>295300</v>
       </c>
       <c r="J72" s="3">
+        <v>253500</v>
+      </c>
+      <c r="K72" s="3">
         <v>163600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1600</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>838400</v>
+        <v>1117100</v>
       </c>
       <c r="E76" s="3">
-        <v>670300</v>
+        <v>833200</v>
       </c>
       <c r="F76" s="3">
-        <v>525200</v>
+        <v>666100</v>
       </c>
       <c r="G76" s="3">
-        <v>624200</v>
+        <v>521900</v>
       </c>
       <c r="H76" s="3">
-        <v>-50500</v>
+        <v>620400</v>
       </c>
       <c r="I76" s="3">
-        <v>412900</v>
+        <v>-50200</v>
       </c>
       <c r="J76" s="3">
+        <v>410300</v>
+      </c>
+      <c r="K76" s="3">
         <v>297500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>500</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>166100</v>
+        <v>287400</v>
       </c>
       <c r="E81" s="3">
-        <v>143600</v>
+        <v>165100</v>
       </c>
       <c r="F81" s="3">
-        <v>-96300</v>
+        <v>142700</v>
       </c>
       <c r="G81" s="3">
-        <v>160700</v>
+        <v>-95700</v>
       </c>
       <c r="H81" s="3">
-        <v>219600</v>
+        <v>159700</v>
       </c>
       <c r="I81" s="3">
-        <v>190700</v>
+        <v>218300</v>
       </c>
       <c r="J81" s="3">
+        <v>189500</v>
+      </c>
+      <c r="K81" s="3">
         <v>155200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1300</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6000</v>
       </c>
-      <c r="F83" s="3">
-        <v>12800</v>
-      </c>
       <c r="G83" s="3">
-        <v>17500</v>
+        <v>12700</v>
       </c>
       <c r="H83" s="3">
-        <v>20600</v>
+        <v>17400</v>
       </c>
       <c r="I83" s="3">
+        <v>20400</v>
+      </c>
+      <c r="J83" s="3">
         <v>3300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>257100</v>
+        <v>299900</v>
       </c>
       <c r="E89" s="3">
-        <v>22000</v>
+        <v>255500</v>
       </c>
       <c r="F89" s="3">
-        <v>39200</v>
+        <v>21900</v>
       </c>
       <c r="G89" s="3">
-        <v>38100</v>
+        <v>39000</v>
       </c>
       <c r="H89" s="3">
-        <v>-550400</v>
+        <v>37900</v>
       </c>
       <c r="I89" s="3">
-        <v>377600</v>
+        <v>-547000</v>
       </c>
       <c r="J89" s="3">
+        <v>375300</v>
+      </c>
+      <c r="K89" s="3">
         <v>293800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1700</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1900</v>
       </c>
-      <c r="G91" s="3">
-        <v>-6700</v>
-      </c>
       <c r="H91" s="3">
-        <v>-19600</v>
+        <v>-6600</v>
       </c>
       <c r="I91" s="3">
-        <v>-9800</v>
+        <v>-19400</v>
       </c>
       <c r="J91" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-4200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E94" s="3">
         <v>7300</v>
       </c>
-      <c r="E94" s="3">
-        <v>-48200</v>
-      </c>
       <c r="F94" s="3">
-        <v>-249800</v>
+        <v>-47900</v>
       </c>
       <c r="G94" s="3">
-        <v>154300</v>
+        <v>-248200</v>
       </c>
       <c r="H94" s="3">
-        <v>458400</v>
+        <v>153400</v>
       </c>
       <c r="I94" s="3">
-        <v>-52100</v>
+        <v>455600</v>
       </c>
       <c r="J94" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-197600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4221,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4007,13 +4240,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-14800</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-84100</v>
+        <v>-14700</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-83600</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,133 +4398,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-68000</v>
+        <v>-78700</v>
       </c>
       <c r="E100" s="3">
-        <v>59400</v>
+        <v>-67600</v>
       </c>
       <c r="F100" s="3">
-        <v>132800</v>
+        <v>59100</v>
       </c>
       <c r="G100" s="3">
-        <v>-159800</v>
+        <v>132000</v>
       </c>
       <c r="H100" s="3">
-        <v>-109600</v>
+        <v>-158800</v>
       </c>
       <c r="I100" s="3">
-        <v>-118100</v>
+        <v>-108900</v>
       </c>
       <c r="J100" s="3">
+        <v>-117400</v>
+      </c>
+      <c r="K100" s="3">
         <v>18800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>16800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1700</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>196800</v>
+        <v>234600</v>
       </c>
       <c r="E102" s="3">
-        <v>33100</v>
+        <v>195500</v>
       </c>
       <c r="F102" s="3">
-        <v>-78100</v>
+        <v>32900</v>
       </c>
       <c r="G102" s="3">
-        <v>32600</v>
+        <v>-77600</v>
       </c>
       <c r="H102" s="3">
-        <v>-201000</v>
+        <v>32400</v>
       </c>
       <c r="I102" s="3">
-        <v>205200</v>
+        <v>-199800</v>
       </c>
       <c r="J102" s="3">
+        <v>204000</v>
+      </c>
+      <c r="K102" s="3">
         <v>119100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>18700</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/YRD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/YRD_YR_FIN.xlsx
@@ -727,25 +727,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>676400</v>
+        <v>690200</v>
       </c>
       <c r="E8" s="3">
-        <v>474500</v>
+        <v>484200</v>
       </c>
       <c r="F8" s="3">
-        <v>618700</v>
+        <v>631300</v>
       </c>
       <c r="G8" s="3">
-        <v>547400</v>
+        <v>558600</v>
       </c>
       <c r="H8" s="3">
-        <v>1212500</v>
+        <v>1237300</v>
       </c>
       <c r="I8" s="3">
-        <v>1645200</v>
+        <v>1678800</v>
       </c>
       <c r="J8" s="3">
-        <v>765900</v>
+        <v>781500</v>
       </c>
       <c r="K8" s="3">
         <v>450100</v>
@@ -772,25 +772,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>134900</v>
+        <v>137600</v>
       </c>
       <c r="E9" s="3">
+        <v>109500</v>
+      </c>
+      <c r="F9" s="3">
         <v>107300</v>
       </c>
-      <c r="F9" s="3">
-        <v>105100</v>
-      </c>
       <c r="G9" s="3">
-        <v>152600</v>
+        <v>155700</v>
       </c>
       <c r="H9" s="3">
-        <v>91900</v>
+        <v>93800</v>
       </c>
       <c r="I9" s="3">
-        <v>146600</v>
+        <v>149600</v>
       </c>
       <c r="J9" s="3">
-        <v>57700</v>
+        <v>58900</v>
       </c>
       <c r="K9" s="3">
         <v>25000</v>
@@ -817,25 +817,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>541500</v>
+        <v>552600</v>
       </c>
       <c r="E10" s="3">
-        <v>367200</v>
+        <v>374700</v>
       </c>
       <c r="F10" s="3">
-        <v>513600</v>
+        <v>524000</v>
       </c>
       <c r="G10" s="3">
-        <v>394800</v>
+        <v>402800</v>
       </c>
       <c r="H10" s="3">
-        <v>1120600</v>
+        <v>1143500</v>
       </c>
       <c r="I10" s="3">
-        <v>1498600</v>
+        <v>1529200</v>
       </c>
       <c r="J10" s="3">
-        <v>708100</v>
+        <v>722600</v>
       </c>
       <c r="K10" s="3">
         <v>425100</v>
@@ -881,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>20600</v>
+        <v>21000</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>3</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>90600</v>
+        <v>92500</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>317900</v>
+        <v>324400</v>
       </c>
       <c r="E17" s="3">
-        <v>271200</v>
+        <v>276700</v>
       </c>
       <c r="F17" s="3">
-        <v>440800</v>
+        <v>449800</v>
       </c>
       <c r="G17" s="3">
-        <v>644900</v>
+        <v>658100</v>
       </c>
       <c r="H17" s="3">
-        <v>1034600</v>
+        <v>1055800</v>
       </c>
       <c r="I17" s="3">
-        <v>1446300</v>
+        <v>1475800</v>
       </c>
       <c r="J17" s="3">
-        <v>534100</v>
+        <v>545000</v>
       </c>
       <c r="K17" s="3">
         <v>299300</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>358500</v>
+        <v>365800</v>
       </c>
       <c r="E18" s="3">
-        <v>203400</v>
+        <v>207500</v>
       </c>
       <c r="F18" s="3">
-        <v>177900</v>
+        <v>181500</v>
       </c>
       <c r="G18" s="3">
-        <v>-97500</v>
+        <v>-99500</v>
       </c>
       <c r="H18" s="3">
-        <v>177900</v>
+        <v>181500</v>
       </c>
       <c r="I18" s="3">
-        <v>199000</v>
+        <v>203000</v>
       </c>
       <c r="J18" s="3">
-        <v>231700</v>
+        <v>236500</v>
       </c>
       <c r="K18" s="3">
         <v>150800</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="E20" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="F20" s="3">
-        <v>-11600</v>
+        <v>-11900</v>
       </c>
       <c r="G20" s="3">
-        <v>-9300</v>
+        <v>-9500</v>
       </c>
       <c r="H20" s="3">
-        <v>14800</v>
+        <v>15100</v>
       </c>
       <c r="I20" s="3">
-        <v>46200</v>
+        <v>47100</v>
       </c>
       <c r="J20" s="3">
-        <v>10400</v>
+        <v>10700</v>
       </c>
       <c r="K20" s="3">
         <v>2500</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>366500</v>
+        <v>373900</v>
       </c>
       <c r="E21" s="3">
-        <v>210200</v>
+        <v>214500</v>
       </c>
       <c r="F21" s="3">
-        <v>172200</v>
+        <v>175700</v>
       </c>
       <c r="G21" s="3">
-        <v>-94200</v>
+        <v>-96100</v>
       </c>
       <c r="H21" s="3">
-        <v>210100</v>
+        <v>214300</v>
       </c>
       <c r="I21" s="3">
-        <v>265500</v>
+        <v>270900</v>
       </c>
       <c r="J21" s="3">
-        <v>245500</v>
+        <v>250500</v>
       </c>
       <c r="K21" s="3">
         <v>154700</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>365500</v>
+        <v>372900</v>
       </c>
       <c r="E23" s="3">
-        <v>206600</v>
+        <v>210800</v>
       </c>
       <c r="F23" s="3">
-        <v>166200</v>
+        <v>169600</v>
       </c>
       <c r="G23" s="3">
-        <v>-106800</v>
+        <v>-109000</v>
       </c>
       <c r="H23" s="3">
-        <v>192700</v>
+        <v>196600</v>
       </c>
       <c r="I23" s="3">
-        <v>245100</v>
+        <v>250100</v>
       </c>
       <c r="J23" s="3">
-        <v>242200</v>
+        <v>247100</v>
       </c>
       <c r="K23" s="3">
         <v>153300</v>
@@ -1366,25 +1366,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>78100</v>
+        <v>79700</v>
       </c>
       <c r="E24" s="3">
-        <v>41500</v>
+        <v>42400</v>
       </c>
       <c r="F24" s="3">
-        <v>23500</v>
+        <v>24000</v>
       </c>
       <c r="G24" s="3">
-        <v>-11100</v>
+        <v>-11400</v>
       </c>
       <c r="H24" s="3">
-        <v>33100</v>
+        <v>33700</v>
       </c>
       <c r="I24" s="3">
-        <v>26800</v>
+        <v>27400</v>
       </c>
       <c r="J24" s="3">
-        <v>52700</v>
+        <v>53700</v>
       </c>
       <c r="K24" s="3">
         <v>-1900</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>287400</v>
+        <v>293300</v>
       </c>
       <c r="E26" s="3">
-        <v>165100</v>
+        <v>168500</v>
       </c>
       <c r="F26" s="3">
-        <v>142700</v>
+        <v>145600</v>
       </c>
       <c r="G26" s="3">
-        <v>-95700</v>
+        <v>-97700</v>
       </c>
       <c r="H26" s="3">
-        <v>159700</v>
+        <v>162900</v>
       </c>
       <c r="I26" s="3">
-        <v>218300</v>
+        <v>222700</v>
       </c>
       <c r="J26" s="3">
-        <v>189500</v>
+        <v>193400</v>
       </c>
       <c r="K26" s="3">
         <v>155200</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>287400</v>
+        <v>293300</v>
       </c>
       <c r="E27" s="3">
-        <v>165100</v>
+        <v>168500</v>
       </c>
       <c r="F27" s="3">
-        <v>142700</v>
+        <v>145600</v>
       </c>
       <c r="G27" s="3">
-        <v>-95700</v>
+        <v>-97700</v>
       </c>
       <c r="H27" s="3">
-        <v>159700</v>
+        <v>162900</v>
       </c>
       <c r="I27" s="3">
-        <v>218300</v>
+        <v>222700</v>
       </c>
       <c r="J27" s="3">
-        <v>189500</v>
+        <v>193400</v>
       </c>
       <c r="K27" s="3">
         <v>155200</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-7000</v>
+        <v>-7100</v>
       </c>
       <c r="E32" s="3">
-        <v>-3200</v>
+        <v>-3300</v>
       </c>
       <c r="F32" s="3">
-        <v>11600</v>
+        <v>11900</v>
       </c>
       <c r="G32" s="3">
-        <v>9300</v>
+        <v>9500</v>
       </c>
       <c r="H32" s="3">
-        <v>-14800</v>
+        <v>-15100</v>
       </c>
       <c r="I32" s="3">
-        <v>-46200</v>
+        <v>-47100</v>
       </c>
       <c r="J32" s="3">
-        <v>-10400</v>
+        <v>-10700</v>
       </c>
       <c r="K32" s="3">
         <v>-2500</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>287400</v>
+        <v>293300</v>
       </c>
       <c r="E33" s="3">
-        <v>165100</v>
+        <v>168500</v>
       </c>
       <c r="F33" s="3">
-        <v>142700</v>
+        <v>145600</v>
       </c>
       <c r="G33" s="3">
-        <v>-95700</v>
+        <v>-97700</v>
       </c>
       <c r="H33" s="3">
-        <v>159700</v>
+        <v>162900</v>
       </c>
       <c r="I33" s="3">
-        <v>218300</v>
+        <v>222700</v>
       </c>
       <c r="J33" s="3">
-        <v>189500</v>
+        <v>193400</v>
       </c>
       <c r="K33" s="3">
         <v>155200</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>287400</v>
+        <v>293300</v>
       </c>
       <c r="E35" s="3">
-        <v>165100</v>
+        <v>168500</v>
       </c>
       <c r="F35" s="3">
-        <v>142700</v>
+        <v>145600</v>
       </c>
       <c r="G35" s="3">
-        <v>-95700</v>
+        <v>-97700</v>
       </c>
       <c r="H35" s="3">
-        <v>159700</v>
+        <v>162900</v>
       </c>
       <c r="I35" s="3">
-        <v>218300</v>
+        <v>222700</v>
       </c>
       <c r="J35" s="3">
-        <v>189500</v>
+        <v>193400</v>
       </c>
       <c r="K35" s="3">
         <v>155200</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>800100</v>
+        <v>816500</v>
       </c>
       <c r="E41" s="3">
-        <v>590200</v>
+        <v>602300</v>
       </c>
       <c r="F41" s="3">
-        <v>395800</v>
+        <v>403800</v>
       </c>
       <c r="G41" s="3">
-        <v>341200</v>
+        <v>348200</v>
       </c>
       <c r="H41" s="3">
-        <v>441800</v>
+        <v>450900</v>
       </c>
       <c r="I41" s="3">
-        <v>360200</v>
+        <v>367500</v>
       </c>
       <c r="J41" s="3">
-        <v>256600</v>
+        <v>261800</v>
       </c>
       <c r="K41" s="3">
         <v>134600</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>190000</v>
+        <v>193900</v>
       </c>
       <c r="E43" s="3">
-        <v>213200</v>
+        <v>217500</v>
       </c>
       <c r="F43" s="3">
-        <v>175200</v>
+        <v>178800</v>
       </c>
       <c r="G43" s="3">
-        <v>159200</v>
+        <v>162400</v>
       </c>
       <c r="H43" s="3">
-        <v>222900</v>
+        <v>227500</v>
       </c>
       <c r="I43" s="3">
-        <v>254000</v>
+        <v>259200</v>
       </c>
       <c r="J43" s="3">
-        <v>19100</v>
+        <v>19500</v>
       </c>
       <c r="K43" s="3">
         <v>4200</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>48400</v>
+        <v>49400</v>
       </c>
       <c r="E45" s="3">
-        <v>32200</v>
+        <v>32900</v>
       </c>
       <c r="F45" s="3">
-        <v>35300</v>
+        <v>36000</v>
       </c>
       <c r="G45" s="3">
-        <v>15100</v>
+        <v>15400</v>
       </c>
       <c r="H45" s="3">
-        <v>27100</v>
+        <v>27600</v>
       </c>
       <c r="I45" s="3">
-        <v>369300</v>
+        <v>376900</v>
       </c>
       <c r="J45" s="3">
-        <v>147700</v>
+        <v>150700</v>
       </c>
       <c r="K45" s="3">
         <v>64900</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>317300</v>
+        <v>323800</v>
       </c>
       <c r="E47" s="3">
-        <v>299900</v>
+        <v>306000</v>
       </c>
       <c r="F47" s="3">
-        <v>422400</v>
+        <v>431000</v>
       </c>
       <c r="G47" s="3">
-        <v>328100</v>
+        <v>334800</v>
       </c>
       <c r="H47" s="3">
-        <v>529200</v>
+        <v>540000</v>
       </c>
       <c r="I47" s="3">
-        <v>944900</v>
+        <v>964200</v>
       </c>
       <c r="J47" s="3">
-        <v>243800</v>
+        <v>248800</v>
       </c>
       <c r="K47" s="3">
         <v>226300</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>14200</v>
+        <v>14500</v>
       </c>
       <c r="E48" s="3">
-        <v>15400</v>
+        <v>15700</v>
       </c>
       <c r="F48" s="3">
-        <v>25300</v>
+        <v>25800</v>
       </c>
       <c r="G48" s="3">
-        <v>34900</v>
+        <v>35600</v>
       </c>
       <c r="H48" s="3">
-        <v>73200</v>
+        <v>74700</v>
       </c>
       <c r="I48" s="3">
-        <v>49200</v>
+        <v>50200</v>
       </c>
       <c r="J48" s="3">
-        <v>11400</v>
+        <v>11600</v>
       </c>
       <c r="K48" s="3">
         <v>4900</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>47100</v>
+        <v>48000</v>
       </c>
       <c r="E52" s="3">
-        <v>23900</v>
+        <v>24400</v>
       </c>
       <c r="F52" s="3">
-        <v>12200</v>
+        <v>12400</v>
       </c>
       <c r="G52" s="3">
-        <v>35100</v>
+        <v>35800</v>
       </c>
       <c r="H52" s="3">
-        <v>16100</v>
+        <v>16400</v>
       </c>
       <c r="I52" s="3">
-        <v>84500</v>
+        <v>86200</v>
       </c>
       <c r="J52" s="3">
-        <v>360200</v>
+        <v>367500</v>
       </c>
       <c r="K52" s="3">
         <v>230000</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1419900</v>
+        <v>1448800</v>
       </c>
       <c r="E54" s="3">
-        <v>1179300</v>
+        <v>1203400</v>
       </c>
       <c r="F54" s="3">
-        <v>1069300</v>
+        <v>1091100</v>
       </c>
       <c r="G54" s="3">
-        <v>926000</v>
+        <v>944900</v>
       </c>
       <c r="H54" s="3">
-        <v>1332500</v>
+        <v>1359700</v>
       </c>
       <c r="I54" s="3">
-        <v>1969000</v>
+        <v>2009200</v>
       </c>
       <c r="J54" s="3">
-        <v>1038800</v>
+        <v>1060000</v>
       </c>
       <c r="K54" s="3">
         <v>665000</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="E57" s="3">
         <v>2000</v>
       </c>
       <c r="F57" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="G57" s="3">
         <v>1400</v>
       </c>
       <c r="H57" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="I57" s="3">
-        <v>42400</v>
+        <v>43300</v>
       </c>
       <c r="J57" s="3">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="K57" s="3">
         <v>1900</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>274200</v>
+        <v>279800</v>
       </c>
       <c r="E59" s="3">
-        <v>218000</v>
+        <v>222500</v>
       </c>
       <c r="F59" s="3">
-        <v>240400</v>
+        <v>245300</v>
       </c>
       <c r="G59" s="3">
-        <v>319700</v>
+        <v>326200</v>
       </c>
       <c r="H59" s="3">
-        <v>374300</v>
+        <v>381900</v>
       </c>
       <c r="I59" s="3">
-        <v>1656800</v>
+        <v>1690700</v>
       </c>
       <c r="J59" s="3">
-        <v>205400</v>
+        <v>209600</v>
       </c>
       <c r="K59" s="3">
         <v>196500</v>
@@ -2845,19 +2845,19 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>106100</v>
+        <v>108300</v>
       </c>
       <c r="F61" s="3">
-        <v>142100</v>
+        <v>145000</v>
       </c>
       <c r="G61" s="3">
-        <v>69100</v>
+        <v>70600</v>
       </c>
       <c r="H61" s="3">
         <v>2600</v>
       </c>
       <c r="I61" s="3">
-        <v>26600</v>
+        <v>27100</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2887,22 +2887,22 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>16900</v>
+        <v>17200</v>
       </c>
       <c r="E62" s="3">
-        <v>11000</v>
+        <v>11200</v>
       </c>
       <c r="F62" s="3">
-        <v>15500</v>
+        <v>15900</v>
       </c>
       <c r="G62" s="3">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="H62" s="3">
-        <v>30200</v>
+        <v>30900</v>
       </c>
       <c r="I62" s="3">
-        <v>67300</v>
+        <v>68600</v>
       </c>
       <c r="J62" s="3">
         <v>1600</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>302800</v>
+        <v>308900</v>
       </c>
       <c r="E66" s="3">
-        <v>346100</v>
+        <v>353200</v>
       </c>
       <c r="F66" s="3">
-        <v>403200</v>
+        <v>411400</v>
       </c>
       <c r="G66" s="3">
-        <v>404100</v>
+        <v>412300</v>
       </c>
       <c r="H66" s="3">
-        <v>712100</v>
+        <v>726700</v>
       </c>
       <c r="I66" s="3">
-        <v>2019200</v>
+        <v>2060500</v>
       </c>
       <c r="J66" s="3">
-        <v>628400</v>
+        <v>641300</v>
       </c>
       <c r="K66" s="3">
         <v>367500</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>412500</v>
+        <v>420900</v>
       </c>
       <c r="E72" s="3">
-        <v>125600</v>
+        <v>128100</v>
       </c>
       <c r="F72" s="3">
-        <v>-34200</v>
+        <v>-34900</v>
       </c>
       <c r="G72" s="3">
-        <v>-173700</v>
+        <v>-177300</v>
       </c>
       <c r="H72" s="3">
-        <v>-73700</v>
+        <v>-75200</v>
       </c>
       <c r="I72" s="3">
-        <v>295300</v>
+        <v>301300</v>
       </c>
       <c r="J72" s="3">
-        <v>253500</v>
+        <v>258700</v>
       </c>
       <c r="K72" s="3">
         <v>163600</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1117100</v>
+        <v>1139900</v>
       </c>
       <c r="E76" s="3">
-        <v>833200</v>
+        <v>850200</v>
       </c>
       <c r="F76" s="3">
-        <v>666100</v>
+        <v>679700</v>
       </c>
       <c r="G76" s="3">
-        <v>521900</v>
+        <v>532600</v>
       </c>
       <c r="H76" s="3">
-        <v>620400</v>
+        <v>633000</v>
       </c>
       <c r="I76" s="3">
-        <v>-50200</v>
+        <v>-51200</v>
       </c>
       <c r="J76" s="3">
-        <v>410300</v>
+        <v>418700</v>
       </c>
       <c r="K76" s="3">
         <v>297500</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>287400</v>
+        <v>293300</v>
       </c>
       <c r="E81" s="3">
-        <v>165100</v>
+        <v>168500</v>
       </c>
       <c r="F81" s="3">
-        <v>142700</v>
+        <v>145600</v>
       </c>
       <c r="G81" s="3">
-        <v>-95700</v>
+        <v>-97700</v>
       </c>
       <c r="H81" s="3">
-        <v>159700</v>
+        <v>162900</v>
       </c>
       <c r="I81" s="3">
-        <v>218300</v>
+        <v>222700</v>
       </c>
       <c r="J81" s="3">
-        <v>189500</v>
+        <v>193400</v>
       </c>
       <c r="K81" s="3">
         <v>155200</v>
@@ -3701,16 +3701,16 @@
         <v>3700</v>
       </c>
       <c r="F83" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="G83" s="3">
-        <v>12700</v>
+        <v>12900</v>
       </c>
       <c r="H83" s="3">
-        <v>17400</v>
+        <v>17700</v>
       </c>
       <c r="I83" s="3">
-        <v>20400</v>
+        <v>20900</v>
       </c>
       <c r="J83" s="3">
         <v>3300</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>299900</v>
+        <v>306100</v>
       </c>
       <c r="E89" s="3">
-        <v>255500</v>
+        <v>260700</v>
       </c>
       <c r="F89" s="3">
-        <v>21900</v>
+        <v>22300</v>
       </c>
       <c r="G89" s="3">
-        <v>39000</v>
+        <v>39800</v>
       </c>
       <c r="H89" s="3">
-        <v>37900</v>
+        <v>38700</v>
       </c>
       <c r="I89" s="3">
-        <v>-547000</v>
+        <v>-558200</v>
       </c>
       <c r="J89" s="3">
-        <v>375300</v>
+        <v>383000</v>
       </c>
       <c r="K89" s="3">
         <v>293800</v>
@@ -4041,13 +4041,13 @@
         <v>-1900</v>
       </c>
       <c r="H91" s="3">
-        <v>-6600</v>
+        <v>-6800</v>
       </c>
       <c r="I91" s="3">
-        <v>-19400</v>
+        <v>-19800</v>
       </c>
       <c r="J91" s="3">
-        <v>-9700</v>
+        <v>-9900</v>
       </c>
       <c r="K91" s="3">
         <v>-4200</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>13800</v>
+        <v>14100</v>
       </c>
       <c r="E94" s="3">
-        <v>7300</v>
+        <v>7400</v>
       </c>
       <c r="F94" s="3">
-        <v>-47900</v>
+        <v>-48900</v>
       </c>
       <c r="G94" s="3">
-        <v>-248200</v>
+        <v>-253300</v>
       </c>
       <c r="H94" s="3">
-        <v>153400</v>
+        <v>156500</v>
       </c>
       <c r="I94" s="3">
-        <v>455600</v>
+        <v>464900</v>
       </c>
       <c r="J94" s="3">
-        <v>-51800</v>
+        <v>-52800</v>
       </c>
       <c r="K94" s="3">
         <v>-197600</v>
@@ -4243,10 +4243,10 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-14700</v>
+        <v>-15000</v>
       </c>
       <c r="J96" s="3">
-        <v>-83600</v>
+        <v>-85300</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-78700</v>
+        <v>-80300</v>
       </c>
       <c r="E100" s="3">
-        <v>-67600</v>
+        <v>-69000</v>
       </c>
       <c r="F100" s="3">
-        <v>59100</v>
+        <v>60300</v>
       </c>
       <c r="G100" s="3">
-        <v>132000</v>
+        <v>134700</v>
       </c>
       <c r="H100" s="3">
-        <v>-158800</v>
+        <v>-162100</v>
       </c>
       <c r="I100" s="3">
-        <v>-108900</v>
+        <v>-111100</v>
       </c>
       <c r="J100" s="3">
-        <v>-117400</v>
+        <v>-119800</v>
       </c>
       <c r="K100" s="3">
         <v>18800</v>
@@ -4456,7 +4456,7 @@
         <v>-500</v>
       </c>
       <c r="E101" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F101" s="3">
         <v>-100</v>
@@ -4471,7 +4471,7 @@
         <v>500</v>
       </c>
       <c r="J101" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="K101" s="3">
         <v>4100</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>234600</v>
+        <v>239400</v>
       </c>
       <c r="E102" s="3">
-        <v>195500</v>
+        <v>199500</v>
       </c>
       <c r="F102" s="3">
-        <v>32900</v>
+        <v>33600</v>
       </c>
       <c r="G102" s="3">
-        <v>-77600</v>
+        <v>-79200</v>
       </c>
       <c r="H102" s="3">
-        <v>32400</v>
+        <v>33100</v>
       </c>
       <c r="I102" s="3">
-        <v>-199800</v>
+        <v>-203800</v>
       </c>
       <c r="J102" s="3">
-        <v>204000</v>
+        <v>208100</v>
       </c>
       <c r="K102" s="3">
         <v>119100</v>

--- a/AAII_Financials/Yearly/YRD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/YRD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>YRD</t>
   </si>
@@ -727,25 +727,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>690200</v>
+        <v>690400</v>
       </c>
       <c r="E8" s="3">
-        <v>484200</v>
+        <v>498000</v>
       </c>
       <c r="F8" s="3">
-        <v>631300</v>
+        <v>704900</v>
       </c>
       <c r="G8" s="3">
-        <v>558600</v>
+        <v>606900</v>
       </c>
       <c r="H8" s="3">
-        <v>1237300</v>
+        <v>1237500</v>
       </c>
       <c r="I8" s="3">
-        <v>1678800</v>
+        <v>1634900</v>
       </c>
       <c r="J8" s="3">
-        <v>781500</v>
+        <v>1772800</v>
       </c>
       <c r="K8" s="3">
         <v>450100</v>
@@ -772,25 +772,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>137600</v>
+        <v>137700</v>
       </c>
       <c r="E9" s="3">
-        <v>109500</v>
+        <v>112600</v>
       </c>
       <c r="F9" s="3">
-        <v>107300</v>
+        <v>119800</v>
       </c>
       <c r="G9" s="3">
-        <v>155700</v>
+        <v>169200</v>
       </c>
       <c r="H9" s="3">
-        <v>93800</v>
+        <v>95500</v>
       </c>
       <c r="I9" s="3">
-        <v>149600</v>
+        <v>154300</v>
       </c>
       <c r="J9" s="3">
-        <v>58900</v>
+        <v>191000</v>
       </c>
       <c r="K9" s="3">
         <v>25000</v>
@@ -817,25 +817,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>552600</v>
+        <v>552700</v>
       </c>
       <c r="E10" s="3">
-        <v>374700</v>
+        <v>385300</v>
       </c>
       <c r="F10" s="3">
-        <v>524000</v>
+        <v>585100</v>
       </c>
       <c r="G10" s="3">
-        <v>402800</v>
+        <v>437700</v>
       </c>
       <c r="H10" s="3">
-        <v>1143500</v>
+        <v>1142000</v>
       </c>
       <c r="I10" s="3">
-        <v>1529200</v>
+        <v>1480600</v>
       </c>
       <c r="J10" s="3">
-        <v>722600</v>
+        <v>1581700</v>
       </c>
       <c r="K10" s="3">
         <v>425100</v>
@@ -883,11 +883,11 @@
       <c r="D12" s="3">
         <v>21000</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
+      <c r="E12" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>32700</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>3</v>
@@ -973,14 +973,14 @@
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>92500</v>
+        <v>100500</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>14100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>18100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>21700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>324400</v>
+        <v>324500</v>
       </c>
       <c r="E17" s="3">
-        <v>276700</v>
+        <v>284600</v>
       </c>
       <c r="F17" s="3">
-        <v>449800</v>
+        <v>502300</v>
       </c>
       <c r="G17" s="3">
-        <v>658100</v>
+        <v>614500</v>
       </c>
       <c r="H17" s="3">
-        <v>1055800</v>
+        <v>1075500</v>
       </c>
       <c r="I17" s="3">
-        <v>1475800</v>
+        <v>1461000</v>
       </c>
       <c r="J17" s="3">
-        <v>545000</v>
+        <v>1778400</v>
       </c>
       <c r="K17" s="3">
         <v>299300</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>365800</v>
+        <v>365900</v>
       </c>
       <c r="E18" s="3">
-        <v>207500</v>
+        <v>213400</v>
       </c>
       <c r="F18" s="3">
-        <v>181500</v>
+        <v>202600</v>
       </c>
       <c r="G18" s="3">
-        <v>-99500</v>
+        <v>-7700</v>
       </c>
       <c r="H18" s="3">
-        <v>181500</v>
+        <v>162000</v>
       </c>
       <c r="I18" s="3">
-        <v>203000</v>
+        <v>173900</v>
       </c>
       <c r="J18" s="3">
-        <v>236500</v>
+        <v>-5600</v>
       </c>
       <c r="K18" s="3">
         <v>150800</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>7100</v>
+        <v>4300</v>
       </c>
       <c r="E20" s="3">
-        <v>3300</v>
+        <v>-7200</v>
       </c>
       <c r="F20" s="3">
-        <v>-11900</v>
+        <v>1700</v>
       </c>
       <c r="G20" s="3">
-        <v>-9500</v>
+        <v>19800</v>
       </c>
       <c r="H20" s="3">
-        <v>15100</v>
+        <v>-27800</v>
       </c>
       <c r="I20" s="3">
-        <v>47100</v>
+        <v>-73300</v>
       </c>
       <c r="J20" s="3">
-        <v>10700</v>
+        <v>-17600</v>
       </c>
       <c r="K20" s="3">
         <v>2500</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>373900</v>
+        <v>362700</v>
       </c>
       <c r="E21" s="3">
-        <v>214500</v>
+        <v>224500</v>
       </c>
       <c r="F21" s="3">
-        <v>175700</v>
+        <v>207800</v>
       </c>
       <c r="G21" s="3">
-        <v>-96100</v>
+        <v>-13400</v>
       </c>
       <c r="H21" s="3">
-        <v>214300</v>
+        <v>207900</v>
       </c>
       <c r="I21" s="3">
-        <v>270900</v>
+        <v>268700</v>
       </c>
       <c r="J21" s="3">
-        <v>250500</v>
+        <v>33700</v>
       </c>
       <c r="K21" s="3">
         <v>154700</v>
@@ -1275,26 +1275,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>11600</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>372900</v>
+        <v>373100</v>
       </c>
       <c r="E23" s="3">
-        <v>210800</v>
+        <v>216800</v>
       </c>
       <c r="F23" s="3">
-        <v>169600</v>
+        <v>189400</v>
       </c>
       <c r="G23" s="3">
-        <v>-109000</v>
+        <v>-118500</v>
       </c>
       <c r="H23" s="3">
-        <v>196600</v>
+        <v>200300</v>
       </c>
       <c r="I23" s="3">
-        <v>250100</v>
+        <v>257900</v>
       </c>
       <c r="J23" s="3">
-        <v>247100</v>
+        <v>29700</v>
       </c>
       <c r="K23" s="3">
         <v>153300</v>
@@ -1369,22 +1369,22 @@
         <v>79700</v>
       </c>
       <c r="E24" s="3">
-        <v>42400</v>
+        <v>43600</v>
       </c>
       <c r="F24" s="3">
-        <v>24000</v>
+        <v>26800</v>
       </c>
       <c r="G24" s="3">
-        <v>-11400</v>
+        <v>-12300</v>
       </c>
       <c r="H24" s="3">
-        <v>33700</v>
+        <v>34400</v>
       </c>
       <c r="I24" s="3">
-        <v>27400</v>
+        <v>28200</v>
       </c>
       <c r="J24" s="3">
-        <v>53700</v>
+        <v>58600</v>
       </c>
       <c r="K24" s="3">
         <v>-1900</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>293300</v>
+        <v>293400</v>
       </c>
       <c r="E26" s="3">
-        <v>168500</v>
+        <v>173200</v>
       </c>
       <c r="F26" s="3">
-        <v>145600</v>
+        <v>162600</v>
       </c>
       <c r="G26" s="3">
-        <v>-97700</v>
+        <v>-106100</v>
       </c>
       <c r="H26" s="3">
-        <v>162900</v>
+        <v>166000</v>
       </c>
       <c r="I26" s="3">
-        <v>222700</v>
+        <v>229700</v>
       </c>
       <c r="J26" s="3">
-        <v>193400</v>
+        <v>-28900</v>
       </c>
       <c r="K26" s="3">
         <v>155200</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>293300</v>
+        <v>293400</v>
       </c>
       <c r="E27" s="3">
-        <v>168500</v>
+        <v>173200</v>
       </c>
       <c r="F27" s="3">
-        <v>145600</v>
+        <v>162600</v>
       </c>
       <c r="G27" s="3">
-        <v>-97700</v>
+        <v>-106100</v>
       </c>
       <c r="H27" s="3">
-        <v>162900</v>
+        <v>166000</v>
       </c>
       <c r="I27" s="3">
-        <v>222700</v>
+        <v>229700</v>
       </c>
       <c r="J27" s="3">
-        <v>193400</v>
+        <v>-28900</v>
       </c>
       <c r="K27" s="3">
         <v>155200</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-7100</v>
+        <v>-4300</v>
       </c>
       <c r="E32" s="3">
-        <v>-3300</v>
+        <v>7200</v>
       </c>
       <c r="F32" s="3">
-        <v>11900</v>
+        <v>-1700</v>
       </c>
       <c r="G32" s="3">
-        <v>9500</v>
+        <v>-19800</v>
       </c>
       <c r="H32" s="3">
-        <v>-15100</v>
+        <v>27800</v>
       </c>
       <c r="I32" s="3">
-        <v>-47100</v>
+        <v>73300</v>
       </c>
       <c r="J32" s="3">
-        <v>-10700</v>
+        <v>17600</v>
       </c>
       <c r="K32" s="3">
         <v>-2500</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>293300</v>
+        <v>293400</v>
       </c>
       <c r="E33" s="3">
-        <v>168500</v>
+        <v>173200</v>
       </c>
       <c r="F33" s="3">
-        <v>145600</v>
+        <v>162600</v>
       </c>
       <c r="G33" s="3">
-        <v>-97700</v>
+        <v>-106100</v>
       </c>
       <c r="H33" s="3">
-        <v>162900</v>
+        <v>166000</v>
       </c>
       <c r="I33" s="3">
-        <v>222700</v>
+        <v>229700</v>
       </c>
       <c r="J33" s="3">
-        <v>193400</v>
+        <v>-28900</v>
       </c>
       <c r="K33" s="3">
         <v>155200</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>293300</v>
+        <v>293400</v>
       </c>
       <c r="E35" s="3">
-        <v>168500</v>
+        <v>173200</v>
       </c>
       <c r="F35" s="3">
-        <v>145600</v>
+        <v>162600</v>
       </c>
       <c r="G35" s="3">
-        <v>-97700</v>
+        <v>-106100</v>
       </c>
       <c r="H35" s="3">
-        <v>162900</v>
+        <v>166000</v>
       </c>
       <c r="I35" s="3">
-        <v>222700</v>
+        <v>229700</v>
       </c>
       <c r="J35" s="3">
-        <v>193400</v>
+        <v>-28900</v>
       </c>
       <c r="K35" s="3">
         <v>155200</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>816500</v>
+        <v>816700</v>
       </c>
       <c r="E41" s="3">
-        <v>602300</v>
+        <v>619400</v>
       </c>
       <c r="F41" s="3">
-        <v>403800</v>
+        <v>450900</v>
       </c>
       <c r="G41" s="3">
-        <v>348200</v>
+        <v>378300</v>
       </c>
       <c r="H41" s="3">
-        <v>450900</v>
+        <v>459300</v>
       </c>
       <c r="I41" s="3">
-        <v>367500</v>
+        <v>379000</v>
       </c>
       <c r="J41" s="3">
-        <v>261800</v>
+        <v>285400</v>
       </c>
       <c r="K41" s="3">
         <v>134600</v>
@@ -2039,19 +2039,19 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>33700</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>11100</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>193900</v>
+        <v>418700</v>
       </c>
       <c r="E43" s="3">
-        <v>217500</v>
+        <v>371000</v>
       </c>
       <c r="F43" s="3">
-        <v>178800</v>
+        <v>620100</v>
       </c>
       <c r="G43" s="3">
-        <v>162400</v>
+        <v>482700</v>
       </c>
       <c r="H43" s="3">
-        <v>227500</v>
+        <v>569300</v>
       </c>
       <c r="I43" s="3">
-        <v>259200</v>
+        <v>1061900</v>
       </c>
       <c r="J43" s="3">
-        <v>19500</v>
+        <v>143000</v>
       </c>
       <c r="K43" s="3">
         <v>4200</v>
@@ -2128,26 +2128,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>49400</v>
+        <v>28700</v>
       </c>
       <c r="E45" s="3">
-        <v>32900</v>
+        <v>40200</v>
       </c>
       <c r="F45" s="3">
-        <v>36000</v>
+        <v>35400</v>
       </c>
       <c r="G45" s="3">
-        <v>15400</v>
+        <v>23000</v>
       </c>
       <c r="H45" s="3">
-        <v>27600</v>
+        <v>93400</v>
       </c>
       <c r="I45" s="3">
-        <v>376900</v>
+        <v>125400</v>
       </c>
       <c r="J45" s="3">
-        <v>150700</v>
+        <v>160700</v>
       </c>
       <c r="K45" s="3">
         <v>64900</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>1361200</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>1067800</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>1158500</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>947900</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>1212300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>1784500</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>870200</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>323800</v>
+        <v>63300</v>
       </c>
       <c r="E47" s="3">
-        <v>306000</v>
+        <v>141400</v>
       </c>
       <c r="F47" s="3">
-        <v>431000</v>
+        <v>28300</v>
       </c>
       <c r="G47" s="3">
-        <v>334800</v>
+        <v>27400</v>
       </c>
       <c r="H47" s="3">
-        <v>540000</v>
+        <v>67200</v>
       </c>
       <c r="I47" s="3">
-        <v>964200</v>
+        <v>201100</v>
       </c>
       <c r="J47" s="3">
-        <v>248800</v>
+        <v>149600</v>
       </c>
       <c r="K47" s="3">
         <v>226300</v>
@@ -2312,22 +2312,22 @@
         <v>14500</v>
       </c>
       <c r="E48" s="3">
-        <v>15700</v>
+        <v>16100</v>
       </c>
       <c r="F48" s="3">
-        <v>25800</v>
+        <v>28900</v>
       </c>
       <c r="G48" s="3">
-        <v>35600</v>
+        <v>38700</v>
       </c>
       <c r="H48" s="3">
-        <v>74700</v>
+        <v>76100</v>
       </c>
       <c r="I48" s="3">
-        <v>50200</v>
+        <v>38700</v>
       </c>
       <c r="J48" s="3">
-        <v>11600</v>
+        <v>12600</v>
       </c>
       <c r="K48" s="3">
         <v>4900</v>
@@ -2488,26 +2488,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>48000</v>
-      </c>
-      <c r="E52" s="3">
-        <v>24400</v>
-      </c>
-      <c r="F52" s="3">
-        <v>12400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>35800</v>
-      </c>
-      <c r="H52" s="3">
-        <v>16400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>86200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>367500</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>230000</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1448800</v>
+        <v>1449300</v>
       </c>
       <c r="E54" s="3">
-        <v>1203400</v>
+        <v>1237600</v>
       </c>
       <c r="F54" s="3">
-        <v>1091100</v>
+        <v>1218300</v>
       </c>
       <c r="G54" s="3">
-        <v>944900</v>
+        <v>1026600</v>
       </c>
       <c r="H54" s="3">
-        <v>1359700</v>
+        <v>1385100</v>
       </c>
       <c r="I54" s="3">
-        <v>2009200</v>
+        <v>2072200</v>
       </c>
       <c r="J54" s="3">
-        <v>1060000</v>
+        <v>1155500</v>
       </c>
       <c r="K54" s="3">
         <v>665000</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4400</v>
+        <v>6200</v>
       </c>
       <c r="E57" s="3">
-        <v>2000</v>
+        <v>5300</v>
       </c>
       <c r="F57" s="3">
-        <v>2700</v>
+        <v>12900</v>
       </c>
       <c r="G57" s="3">
-        <v>1400</v>
+        <v>27700</v>
       </c>
       <c r="H57" s="3">
-        <v>6100</v>
+        <v>17800</v>
       </c>
       <c r="I57" s="3">
-        <v>43300</v>
+        <v>1232300</v>
       </c>
       <c r="J57" s="3">
-        <v>4800</v>
+        <v>16200</v>
       </c>
       <c r="K57" s="3">
         <v>1900</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>31300</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>58600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>65800</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>27800</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>279800</v>
+        <v>153700</v>
       </c>
       <c r="E59" s="3">
-        <v>222500</v>
+        <v>106800</v>
       </c>
       <c r="F59" s="3">
-        <v>245300</v>
+        <v>67000</v>
       </c>
       <c r="G59" s="3">
-        <v>326200</v>
+        <v>117100</v>
       </c>
       <c r="H59" s="3">
-        <v>381900</v>
+        <v>190000</v>
       </c>
       <c r="I59" s="3">
-        <v>1690700</v>
+        <v>113800</v>
       </c>
       <c r="J59" s="3">
-        <v>209600</v>
+        <v>121400</v>
       </c>
       <c r="K59" s="3">
         <v>196500</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>203600</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>211100</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>239600</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>323700</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>367200</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1509900</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>216200</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2842,22 +2842,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E61" s="3">
-        <v>108300</v>
+        <v>113800</v>
       </c>
       <c r="F61" s="3">
-        <v>145000</v>
+        <v>168300</v>
       </c>
       <c r="G61" s="3">
-        <v>70600</v>
+        <v>79600</v>
       </c>
       <c r="H61" s="3">
-        <v>2600</v>
+        <v>15400</v>
       </c>
       <c r="I61" s="3">
-        <v>27100</v>
+        <v>28000</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>79900</v>
+      </c>
+      <c r="E62" s="3">
         <v>17200</v>
       </c>
-      <c r="E62" s="3">
-        <v>11200</v>
-      </c>
       <c r="F62" s="3">
-        <v>15900</v>
+        <v>31900</v>
       </c>
       <c r="G62" s="3">
-        <v>5500</v>
+        <v>30900</v>
       </c>
       <c r="H62" s="3">
-        <v>30900</v>
+        <v>274700</v>
       </c>
       <c r="I62" s="3">
-        <v>68600</v>
+        <v>433600</v>
       </c>
       <c r="J62" s="3">
-        <v>1600</v>
+        <v>446800</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>308900</v>
+        <v>309000</v>
       </c>
       <c r="E66" s="3">
-        <v>353200</v>
+        <v>363200</v>
       </c>
       <c r="F66" s="3">
-        <v>411400</v>
+        <v>459300</v>
       </c>
       <c r="G66" s="3">
-        <v>412300</v>
+        <v>448000</v>
       </c>
       <c r="H66" s="3">
-        <v>726700</v>
+        <v>740300</v>
       </c>
       <c r="I66" s="3">
-        <v>2060500</v>
+        <v>2125000</v>
       </c>
       <c r="J66" s="3">
-        <v>641300</v>
+        <v>699100</v>
       </c>
       <c r="K66" s="3">
         <v>367500</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>420900</v>
+        <v>421000</v>
       </c>
       <c r="E72" s="3">
-        <v>128100</v>
+        <v>131800</v>
       </c>
       <c r="F72" s="3">
-        <v>-34900</v>
+        <v>-39000</v>
       </c>
       <c r="G72" s="3">
-        <v>-177300</v>
+        <v>-192600</v>
       </c>
       <c r="H72" s="3">
-        <v>-75200</v>
+        <v>-76600</v>
       </c>
       <c r="I72" s="3">
-        <v>301300</v>
+        <v>-243300</v>
       </c>
       <c r="J72" s="3">
-        <v>258700</v>
+        <v>282000</v>
       </c>
       <c r="K72" s="3">
         <v>163600</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1139900</v>
+        <v>1140300</v>
       </c>
       <c r="E76" s="3">
-        <v>850200</v>
+        <v>874400</v>
       </c>
       <c r="F76" s="3">
-        <v>679700</v>
+        <v>759000</v>
       </c>
       <c r="G76" s="3">
-        <v>532600</v>
+        <v>578600</v>
       </c>
       <c r="H76" s="3">
-        <v>633000</v>
+        <v>644900</v>
       </c>
       <c r="I76" s="3">
-        <v>-51200</v>
+        <v>-52800</v>
       </c>
       <c r="J76" s="3">
-        <v>418700</v>
+        <v>456500</v>
       </c>
       <c r="K76" s="3">
         <v>297500</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>293300</v>
+        <v>293400</v>
       </c>
       <c r="E81" s="3">
-        <v>168500</v>
+        <v>173200</v>
       </c>
       <c r="F81" s="3">
-        <v>145600</v>
+        <v>162600</v>
       </c>
       <c r="G81" s="3">
-        <v>-97700</v>
+        <v>-106100</v>
       </c>
       <c r="H81" s="3">
-        <v>162900</v>
+        <v>166000</v>
       </c>
       <c r="I81" s="3">
-        <v>222700</v>
+        <v>229700</v>
       </c>
       <c r="J81" s="3">
-        <v>193400</v>
+        <v>-28900</v>
       </c>
       <c r="K81" s="3">
         <v>155200</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1000</v>
+        <v>3600</v>
       </c>
       <c r="E83" s="3">
-        <v>3700</v>
+        <v>7700</v>
       </c>
       <c r="F83" s="3">
-        <v>6100</v>
+        <v>22000</v>
       </c>
       <c r="G83" s="3">
-        <v>12900</v>
+        <v>50200</v>
       </c>
       <c r="H83" s="3">
-        <v>17700</v>
+        <v>56700</v>
       </c>
       <c r="I83" s="3">
-        <v>20900</v>
+        <v>21500</v>
       </c>
       <c r="J83" s="3">
-        <v>3300</v>
+        <v>21700</v>
       </c>
       <c r="K83" s="3">
         <v>1500</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>306100</v>
+        <v>306200</v>
       </c>
       <c r="E89" s="3">
-        <v>260700</v>
+        <v>268100</v>
       </c>
       <c r="F89" s="3">
-        <v>22300</v>
+        <v>24900</v>
       </c>
       <c r="G89" s="3">
-        <v>39800</v>
+        <v>43200</v>
       </c>
       <c r="H89" s="3">
-        <v>38700</v>
+        <v>39400</v>
       </c>
       <c r="I89" s="3">
-        <v>-558200</v>
+        <v>-575600</v>
       </c>
       <c r="J89" s="3">
-        <v>383000</v>
+        <v>28300</v>
       </c>
       <c r="K89" s="3">
         <v>293800</v>
@@ -4035,19 +4035,19 @@
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>-1300</v>
+        <v>-1500</v>
       </c>
       <c r="G91" s="3">
-        <v>-1900</v>
+        <v>-2100</v>
       </c>
       <c r="H91" s="3">
-        <v>-6800</v>
+        <v>-6900</v>
       </c>
       <c r="I91" s="3">
-        <v>-19800</v>
+        <v>-20500</v>
       </c>
       <c r="J91" s="3">
-        <v>-9900</v>
+        <v>-33500</v>
       </c>
       <c r="K91" s="3">
         <v>-4200</v>
@@ -4167,22 +4167,22 @@
         <v>14100</v>
       </c>
       <c r="E94" s="3">
-        <v>7400</v>
+        <v>7600</v>
       </c>
       <c r="F94" s="3">
-        <v>-48900</v>
+        <v>-54500</v>
       </c>
       <c r="G94" s="3">
-        <v>-253300</v>
+        <v>-275200</v>
       </c>
       <c r="H94" s="3">
-        <v>156500</v>
+        <v>159400</v>
       </c>
       <c r="I94" s="3">
-        <v>464900</v>
+        <v>479500</v>
       </c>
       <c r="J94" s="3">
-        <v>-52800</v>
+        <v>-179300</v>
       </c>
       <c r="K94" s="3">
         <v>-197600</v>
@@ -4243,10 +4243,10 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-15000</v>
+        <v>15500</v>
       </c>
       <c r="J96" s="3">
-        <v>-85300</v>
+        <v>93000</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4411,22 +4411,22 @@
         <v>-80300</v>
       </c>
       <c r="E100" s="3">
-        <v>-69000</v>
+        <v>-70900</v>
       </c>
       <c r="F100" s="3">
-        <v>60300</v>
+        <v>67300</v>
       </c>
       <c r="G100" s="3">
-        <v>134700</v>
+        <v>146300</v>
       </c>
       <c r="H100" s="3">
-        <v>-162100</v>
+        <v>-165100</v>
       </c>
       <c r="I100" s="3">
-        <v>-111100</v>
+        <v>-114600</v>
       </c>
       <c r="J100" s="3">
-        <v>-119800</v>
+        <v>406100</v>
       </c>
       <c r="K100" s="3">
         <v>18800</v>
@@ -4471,7 +4471,7 @@
         <v>500</v>
       </c>
       <c r="J101" s="3">
-        <v>-2300</v>
+        <v>-2500</v>
       </c>
       <c r="K101" s="3">
         <v>4100</v>
@@ -4501,22 +4501,22 @@
         <v>239400</v>
       </c>
       <c r="E102" s="3">
-        <v>199500</v>
+        <v>205200</v>
       </c>
       <c r="F102" s="3">
-        <v>33600</v>
+        <v>37500</v>
       </c>
       <c r="G102" s="3">
-        <v>-79200</v>
+        <v>-86100</v>
       </c>
       <c r="H102" s="3">
-        <v>33100</v>
+        <v>33700</v>
       </c>
       <c r="I102" s="3">
-        <v>-203800</v>
+        <v>-210200</v>
       </c>
       <c r="J102" s="3">
-        <v>208100</v>
+        <v>252600</v>
       </c>
       <c r="K102" s="3">
         <v>119100</v>

--- a/AAII_Financials/Yearly/YRD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/YRD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>YRD</t>
   </si>
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>795400</v>
+      </c>
+      <c r="E8" s="3">
         <v>690400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>498000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>704900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>606900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1237500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1634900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1772800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>450100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>30000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>500</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E9" s="3">
         <v>137700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>112600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>119800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>169200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>95500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>154300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>191000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>25000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>674500</v>
+      </c>
+      <c r="E10" s="3">
         <v>552700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>385300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>585100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>437700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1142000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1480600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1581700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>425100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>27800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>300</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,23 +887,24 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E12" s="3">
         <v>21000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>22000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>32700</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,9 +980,12 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -979,12 +998,12 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>100500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1000,8 +1019,8 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1009,36 +1028,39 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E15" s="3">
         <v>1000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>18100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>21500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21700</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>450700</v>
+      </c>
+      <c r="E17" s="3">
         <v>324500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>284600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>502300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>614500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1075500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1461000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1778400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>299300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1800</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>344700</v>
+      </c>
+      <c r="E18" s="3">
         <v>365900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>213400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>202600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>162000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>173900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>150800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1300</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,113 +1212,120 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>104200</v>
+      </c>
+      <c r="E20" s="3">
         <v>4300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>19800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-27800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-73300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-17600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>241800</v>
+      </c>
+      <c r="E21" s="3">
         <v>362700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>224500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>207800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-13400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>207900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>268700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>33700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>154700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1300</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
         <v>3800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>11600</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1296,8 +1335,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1314,99 +1353,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>255000</v>
+      </c>
+      <c r="E23" s="3">
         <v>373100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>216800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>189400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-118500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>200300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>257900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>29700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>153300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1300</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E24" s="3">
         <v>79700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>43600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>26800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-12300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>34400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>28200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>58600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2900</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>216800</v>
+      </c>
+      <c r="E26" s="3">
         <v>293400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>173200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>162600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-106100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>166000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>229700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-28900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>155200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1300</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>216800</v>
+      </c>
+      <c r="E27" s="3">
         <v>293400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>173200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>162600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-106100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>166000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>229700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-28900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>155200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1300</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-104200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-19800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>27800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>73300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>17600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>216800</v>
+      </c>
+      <c r="E33" s="3">
         <v>293400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>173200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>162600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-106100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>166000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>229700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-28900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>155200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1300</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>216800</v>
+      </c>
+      <c r="E35" s="3">
         <v>293400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>173200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>162600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-106100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>166000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>229700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-28900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>155200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1300</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,74 +2073,78 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>526300</v>
+      </c>
+      <c r="E41" s="3">
         <v>816700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>619400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>450900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>378300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>459300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>379000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>285400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>134600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18800</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
       <c r="N41" s="3">
         <v>0</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
+      <c r="O41" s="3">
+        <v>0</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E42" s="3">
         <v>57000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>23600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>33700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>11100</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -2077,54 +2166,60 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>740200</v>
+      </c>
+      <c r="E43" s="3">
         <v>418700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>371000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>620100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>482700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>569300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1061900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>143000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>600</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2149,8 +2244,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2167,81 +2262,87 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E45" s="3">
         <v>28700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>40200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>35400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>23000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>93400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>125400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>160700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>64900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>100</v>
       </c>
       <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
+      <c r="O45" s="3">
+        <v>100</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1701200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1361200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1067800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1158500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>947900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1212300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1784500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>870200</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2257,99 +2358,108 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E47" s="3">
         <v>63300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>141400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>28300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>27400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>67200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>201100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>149600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>226300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>100</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>0</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E48" s="3">
         <v>14500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>28900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>76100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>38700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>100</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
+      <c r="O48" s="3">
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,9 +2598,12 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2509,15 +2628,15 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
         <v>230000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14600</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2527,9 +2646,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1778700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1449300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1237600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1218300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1026600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1385100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2072200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1155500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>665000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>48600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>800</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,41 +2785,42 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E57" s="3">
         <v>6200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>27700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1232300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,36 +2830,39 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>2700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>31300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>58600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>65800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>27800</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>7700</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2745,81 +2878,87 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E59" s="3">
         <v>153700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>106800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>67000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>117100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>190000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>113800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>121400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>196500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>245900</v>
+      </c>
+      <c r="E60" s="3">
         <v>203600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>211100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>239600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>323700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>367200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1509900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>216200</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2835,33 +2974,36 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E61" s="3">
         <v>700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>113800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>168300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>79600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>28000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2880,36 +3022,39 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>212900</v>
+      </c>
+      <c r="E62" s="3">
         <v>79900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>17200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>31900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>30900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>274700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>433600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>446800</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>471300</v>
+      </c>
+      <c r="E66" s="3">
         <v>309000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>363200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>459300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>448000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>740300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2125000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>699100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>367500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>300</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>607600</v>
+      </c>
+      <c r="E72" s="3">
         <v>421000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>131800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-39000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-192600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-76600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-243300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>282000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>163600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1600</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1307300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1140300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>874400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>759000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>578600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>644900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-52800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>456500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>297500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>500</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>216800</v>
+      </c>
+      <c r="E81" s="3">
         <v>293400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>173200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>162600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-106100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>166000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>229700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-28900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>155200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1300</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E83" s="3">
         <v>3600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>22000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>50200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>56700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>195100</v>
+      </c>
+      <c r="E89" s="3">
         <v>306200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>268100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>43200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>39400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-575600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>28300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>293800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1700</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-33500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-426500</v>
+      </c>
+      <c r="E94" s="3">
         <v>14100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>7600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-54500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-275200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>159400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>479500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-179300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-197600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,8 +4454,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4243,14 +4476,14 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>15500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>93000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,142 +4643,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-80300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-70900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>67300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>146300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-165100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-114600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>406100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>18800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>16800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1700</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-268100</v>
+      </c>
+      <c r="E102" s="3">
         <v>239400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>205200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>37500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-86100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>33700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-210200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>252600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>119100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>18700</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/YRD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/YRD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
   <si>
     <t>YRD</t>
   </si>
@@ -1106,10 +1106,10 @@
         <v>450700</v>
       </c>
       <c r="E17" s="3">
-        <v>324500</v>
+        <v>320700</v>
       </c>
       <c r="F17" s="3">
-        <v>284600</v>
+        <v>281500</v>
       </c>
       <c r="G17" s="3">
         <v>502300</v>
@@ -1154,10 +1154,10 @@
         <v>344700</v>
       </c>
       <c r="E18" s="3">
-        <v>365900</v>
+        <v>369700</v>
       </c>
       <c r="F18" s="3">
-        <v>213400</v>
+        <v>216500</v>
       </c>
       <c r="G18" s="3">
         <v>202600</v>
@@ -1222,10 +1222,10 @@
         <v>104200</v>
       </c>
       <c r="E20" s="3">
-        <v>4300</v>
+        <v>8100</v>
       </c>
       <c r="F20" s="3">
-        <v>-7200</v>
+        <v>-4100</v>
       </c>
       <c r="G20" s="3">
         <v>1700</v>
@@ -1798,10 +1798,10 @@
         <v>-104200</v>
       </c>
       <c r="E32" s="3">
-        <v>-4300</v>
+        <v>-8100</v>
       </c>
       <c r="F32" s="3">
-        <v>7200</v>
+        <v>4100</v>
       </c>
       <c r="G32" s="3">
         <v>-1700</v>
@@ -2128,7 +2128,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>10600</v>
+        <v>188000</v>
       </c>
       <c r="E42" s="3">
         <v>57000</v>
@@ -2176,7 +2176,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>740200</v>
+        <v>589700</v>
       </c>
       <c r="E43" s="3">
         <v>418700</v>
@@ -2272,10 +2272,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>65000</v>
+        <v>224500</v>
       </c>
       <c r="E45" s="3">
-        <v>28700</v>
+        <v>28000</v>
       </c>
       <c r="F45" s="3">
         <v>40200</v>
@@ -2320,10 +2320,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1701200</v>
+        <v>1572000</v>
       </c>
       <c r="E46" s="3">
-        <v>1361200</v>
+        <v>1360600</v>
       </c>
       <c r="F46" s="3">
         <v>1067800</v>
@@ -2464,10 +2464,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -2607,8 +2607,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>128600</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>3</v>
@@ -2792,7 +2792,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5900</v>
+        <v>23600</v>
       </c>
       <c r="E57" s="3">
         <v>6200</v>
@@ -2840,7 +2840,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E58" s="3">
         <v>2700</v>
@@ -2888,7 +2888,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>17800</v>
+        <v>160100</v>
       </c>
       <c r="E59" s="3">
         <v>153700</v>
@@ -2936,7 +2936,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>245900</v>
+        <v>237400</v>
       </c>
       <c r="E60" s="3">
         <v>203600</v>
@@ -2984,7 +2984,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="E61" s="3">
         <v>700</v>
@@ -3032,7 +3032,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>212900</v>
+        <v>223500</v>
       </c>
       <c r="E62" s="3">
         <v>79900</v>
@@ -3893,7 +3893,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1200</v>
+        <v>3900</v>
       </c>
       <c r="E83" s="3">
         <v>3600</v>
@@ -4248,8 +4248,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-1300</v>
       </c>
       <c r="E91" s="3">
         <v>-600</v>
@@ -4461,7 +4461,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>16800</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/YRD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/YRD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>YRD</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>817700</v>
+      </c>
+      <c r="E8" s="3">
         <v>795400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>690400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>498000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>704900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>606900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1237500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1634900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1772800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>450100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>30000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>500</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>112400</v>
+      </c>
+      <c r="E9" s="3">
         <v>121000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>137700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>112600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>119800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>169200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>95500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>154300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>191000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>25000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>705300</v>
+      </c>
+      <c r="E10" s="3">
         <v>674500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>552700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>385300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>585100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>437700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1142000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1480600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1581700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>425100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>27800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>300</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,26 +900,27 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>58100</v>
+      </c>
+      <c r="E12" s="3">
         <v>56400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>22000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>32700</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,9 +999,12 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1001,12 +1020,12 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>100500</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1022,8 +1041,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1031,39 +1050,42 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E15" s="3">
         <v>1200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>14100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>18100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>21700</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1079,9 +1101,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>511100</v>
+      </c>
+      <c r="E17" s="3">
         <v>450700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>320700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>281500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>502300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>614500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1075500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1461000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1778400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>299300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1800</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>306600</v>
+      </c>
+      <c r="E18" s="3">
         <v>344700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>369700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>216500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>202600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>162000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>173900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>150800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1300</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,104 +1245,111 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>325100</v>
+      </c>
+      <c r="E20" s="3">
         <v>104200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>19800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-27800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-73300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-17600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E21" s="3">
         <v>241800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>362700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>224500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>207800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-13400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>207900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>268700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>33700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>154700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1320,15 +1359,15 @@
       <c r="E22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3">
         <v>3800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11600</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1338,8 +1377,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1356,105 +1395,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E23" s="3">
         <v>255000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>373100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>216800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>189400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-118500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>200300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>257900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>29700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>153300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E24" s="3">
         <v>38200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>79700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>43600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>26800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-12300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>34400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>28200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>58600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2900</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E26" s="3">
         <v>216800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>293400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>173200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>162600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-106100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>166000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>229700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>155200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1300</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E27" s="3">
         <v>216800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>293400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>173200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>162600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-106100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>166000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>229700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>155200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1300</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-325100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-104200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-19800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>27800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>73300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>17600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E33" s="3">
         <v>216800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>293400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>173200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>162600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-106100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>166000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>229700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>155200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1300</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E35" s="3">
         <v>216800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>293400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>173200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>162600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-106100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>166000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>229700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>155200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1300</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,80 +2159,84 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>478700</v>
+      </c>
+      <c r="E41" s="3">
         <v>526300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>816700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>619400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>450900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>378300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>459300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>379000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>285400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>134600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>18800</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
       <c r="O41" s="3">
         <v>0</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
+      <c r="P41" s="3">
+        <v>0</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>214500</v>
+      </c>
+      <c r="E42" s="3">
         <v>188000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>57000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>23600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>33700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11100</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -2169,57 +2258,63 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>589700</v>
+        <v>657000</v>
       </c>
       <c r="E43" s="3">
+        <v>591600</v>
+      </c>
+      <c r="F43" s="3">
         <v>418700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>371000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>620100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>482700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>569300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1061900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>143000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>600</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2247,8 +2342,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2265,87 +2360,93 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>224500</v>
+        <v>280600</v>
       </c>
       <c r="E45" s="3">
-        <v>28000</v>
+        <v>222300</v>
       </c>
       <c r="F45" s="3">
-        <v>40200</v>
+        <v>25900</v>
       </c>
       <c r="G45" s="3">
+        <v>35500</v>
+      </c>
+      <c r="H45" s="3">
         <v>35400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>23000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>93400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>125400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>160700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>64900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5500</v>
-      </c>
-      <c r="N45" s="3">
-        <v>100</v>
       </c>
       <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
+      <c r="P45" s="3">
+        <v>100</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1572000</v>
+        <v>1725700</v>
       </c>
       <c r="E46" s="3">
-        <v>1360600</v>
+        <v>1571700</v>
       </c>
       <c r="F46" s="3">
-        <v>1067800</v>
+        <v>1358400</v>
       </c>
       <c r="G46" s="3">
+        <v>1063100</v>
+      </c>
+      <c r="H46" s="3">
         <v>1158500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>947900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1212300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1784500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>870200</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2361,105 +2462,114 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>70200</v>
+      </c>
+      <c r="E47" s="3">
         <v>50600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>63300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>141400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>28300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>27400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>67200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>201100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>149600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>226300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>100</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>0</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E48" s="3">
         <v>16200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>16100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>38700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>76100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>38700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>100</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
+      <c r="P48" s="3">
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2470,7 +2580,7 @@
         <v>700</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G49" s="3">
         <v>0</v>
@@ -2505,9 +2615,12 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,23 +2717,26 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>128600</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
+        <v>67500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>128900</v>
+      </c>
+      <c r="F52" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G52" s="3">
+        <v>4700</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -2631,15 +2750,15 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3">
         <v>230000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14600</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,9 +2768,12 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1923700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1778700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1449300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1237600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1218300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1026600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1385100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2072200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1155500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>665000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>48600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>800</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,44 +2915,45 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E57" s="3">
         <v>23600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>27700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1232300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2833,39 +2963,42 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E58" s="3">
         <v>2100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>31300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>58600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>65800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>27800</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>7700</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -2881,87 +3014,93 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>160100</v>
+        <v>30100</v>
       </c>
       <c r="E59" s="3">
+        <v>163700</v>
+      </c>
+      <c r="F59" s="3">
         <v>153700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>106800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>67000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>117100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>190000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>113800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>121400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>196500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>300</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>237400</v>
+        <v>72000</v>
       </c>
       <c r="E60" s="3">
+        <v>242000</v>
+      </c>
+      <c r="F60" s="3">
         <v>203600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>211100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>239600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>323700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>367200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1509900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>216200</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2977,36 +3116,39 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E61" s="3">
         <v>3500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>113800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>168300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>79600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>28000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3025,39 +3167,42 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>223500</v>
+        <v>519000</v>
       </c>
       <c r="E62" s="3">
+        <v>218800</v>
+      </c>
+      <c r="F62" s="3">
         <v>79900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>17200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>31900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>30900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>274700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>433600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>446800</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3073,9 +3218,12 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>598000</v>
+      </c>
+      <c r="E66" s="3">
         <v>471300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>309000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>363200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>459300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>448000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>740300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2125000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>699100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>367500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>300</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>601300</v>
+      </c>
+      <c r="E72" s="3">
         <v>607600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>421000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>131800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-39000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-192600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-76600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-243300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>282000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>163600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1600</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1325600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1307300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1140300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>874400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>759000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>578600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>644900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-52800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>456500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>297500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>500</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E81" s="3">
         <v>216800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>293400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>173200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>162600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-106100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>166000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>229700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>155200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1300</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E83" s="3">
         <v>3900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>22000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>50200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>56700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>100600</v>
+      </c>
+      <c r="E89" s="3">
         <v>195100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>306200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>268100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>43200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>39400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-575600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>28300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>293800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-33500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-225300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-426500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>14100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>7600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-54500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-275200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>159400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>479500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-179300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-197600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,17 +4687,18 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E96" s="3">
         <v>16800</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -4479,14 +4712,14 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>15500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>93000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4502,9 +4735,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,151 +4888,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-38000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-80300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-70900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>67300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>146300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-165100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-114600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>406100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>18800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>16800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1700</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>1300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-268100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>239400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>205200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>37500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-86100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>33700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-210200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>252600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>119100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>18700</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
